--- a/Baseline_docs/Time Sheet.xlsx
+++ b/Baseline_docs/Time Sheet.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://neumont-my.sharepoint.com/personal/wskinner_student_neumont_edu/Documents/Documents/Year 4/1/project/Capstone/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wskinner\On Drive Files\Git\Secure-Multi-Layer-Network-Project---Capstone\Baseline_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="199" documentId="11_F25DC773A252ABDACC10488959D942DE5BDE58EB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF69AB99-792D-4641-801C-C2E7CC86DF78}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{293FBC09-3151-4D34-BEB6-C74A6AEC540B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Day</t>
   </si>
@@ -66,6 +66,12 @@
   </si>
   <si>
     <t>Hour Percent</t>
+  </si>
+  <si>
+    <t>Hours Needed</t>
+  </si>
+  <si>
+    <t>Hours Met</t>
   </si>
 </sst>
 </file>
@@ -110,13 +116,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -127,15 +130,14 @@
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -144,7 +146,13 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="14">
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -164,9 +172,11 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
@@ -178,7 +188,10 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -196,22 +209,18 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AECFD94D-BC69-43FE-8A1B-A8548D9C1CB8}" name="Table1" displayName="Table1" ref="A2:E57" totalsRowShown="0" headerRowDxfId="10">
-  <autoFilter ref="A2:E57" xr:uid="{AECFD94D-BC69-43FE-8A1B-A8548D9C1CB8}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AECFD94D-BC69-43FE-8A1B-A8548D9C1CB8}" name="Table1" displayName="Table1" ref="A2:E75" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
+  <autoFilter ref="A2:E75" xr:uid="{AECFD94D-BC69-43FE-8A1B-A8548D9C1CB8}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{7D80F612-B207-4202-A1B2-4CDD0B31BE04}" name="Day" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{809082CE-E596-42B5-B407-A4E321ECCB56}" name="Start" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{387E5ED8-33C5-4EC7-A1F3-CE1B1DDAF190}" name="Stop" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{A72F3DB0-D92C-4679-A812-253243311EF0}" name="Minutes " dataDxfId="6">
-      <calculatedColumnFormula>MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]))</calculatedColumnFormula>
+    <tableColumn id="1" xr3:uid="{7D80F612-B207-4202-A1B2-4CDD0B31BE04}" name="Day" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{809082CE-E596-42B5-B407-A4E321ECCB56}" name="Start" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{387E5ED8-33C5-4EC7-A1F3-CE1B1DDAF190}" name="Stop" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{A72F3DB0-D92C-4679-A812-253243311EF0}" name="Minutes " dataDxfId="8">
+      <calculatedColumnFormula>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{CE4B143E-B608-48C4-8FCC-14B01E692DCB}" name="Hours" dataDxfId="5">
-      <calculatedColumnFormula>HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])</calculatedColumnFormula>
+    <tableColumn id="5" xr3:uid="{CE4B143E-B608-48C4-8FCC-14B01E692DCB}" name="Hours" dataDxfId="7">
+      <calculatedColumnFormula>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -219,18 +228,22 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{BCDE2B7C-F4D9-498C-BDF8-E77B124E5F78}" name="Table2" displayName="Table2" ref="J2:L3" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
-  <autoFilter ref="J2:L3" xr:uid="{BCDE2B7C-F4D9-498C-BDF8-E77B124E5F78}"/>
-  <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{25609316-2FC7-4598-9816-D773B5ABDED5}" name="Total Minutes" dataDxfId="2">
-      <calculatedColumnFormula>SUM(D:D) + (K3*60)</calculatedColumnFormula>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{BCDE2B7C-F4D9-498C-BDF8-E77B124E5F78}" name="Table2" displayName="Table2" ref="G2:K3" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+  <autoFilter ref="G2:K3" xr:uid="{BCDE2B7C-F4D9-498C-BDF8-E77B124E5F78}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{25609316-2FC7-4598-9816-D773B5ABDED5}" name="Total Minutes" dataDxfId="4">
+      <calculatedColumnFormula>SUM(D:D) + (H3*60)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C48BBBC8-9BDB-469A-A714-B3361A5491E0}" name="Total Hours" dataDxfId="1">
+    <tableColumn id="2" xr3:uid="{C48BBBC8-9BDB-469A-A714-B3361A5491E0}" name="Total Hours" dataDxfId="3">
       <calculatedColumnFormula>SUM(E:E)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{B3EDE8C1-FEE6-4401-BAF1-7A6A74F4FE86}" name="Hour Percent" dataDxfId="0">
+    <tableColumn id="3" xr3:uid="{B3EDE8C1-FEE6-4401-BAF1-7A6A74F4FE86}" name="Hour Percent" dataDxfId="2">
       <calculatedColumnFormula>Table2[[#This Row],[Total Minutes]]/60</calculatedColumnFormula>
     </tableColumn>
+    <tableColumn id="4" xr3:uid="{8FB2D23B-72D8-4504-BE1A-A47C565D5166}" name="Hours Met" dataDxfId="1">
+      <calculatedColumnFormula>IF(Table2[[#This Row],[Hour Percent]] &gt;= Table2[[#This Row],[Hours Needed]], "Hours have been met", "More hours needed")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{643AEBD5-F2A2-4877-923F-2A6F10830FA5}" name="Hours Needed" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -499,27 +512,39 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L57"/>
+  <dimension ref="A1:K75"/>
   <sheetFormatPr defaultColWidth="16" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="5" max="5" width="16" style="6"/>
+    <col min="1" max="1" width="14.36328125" style="1" customWidth="1"/>
+    <col min="2" max="3" width="16" style="1"/>
+    <col min="4" max="4" width="11.54296875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.54296875" style="5" customWidth="1"/>
+    <col min="6" max="6" width="3.7265625" style="1" customWidth="1"/>
+    <col min="7" max="9" width="16" style="1"/>
+    <col min="10" max="10" width="22.90625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="17.26953125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="16" style="1"/>
+    <col min="13" max="13" width="22.08984375" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="16" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="J1" s="9" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="G1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -532,874 +557,1159 @@
       <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A3" s="7">
+        <v>46027</v>
+      </c>
+      <c r="B3" s="2">
+        <v>46027.625</v>
+      </c>
+      <c r="C3" s="2">
+        <v>46027.667568055556</v>
+      </c>
+      <c r="D3" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>1</v>
+      </c>
+      <c r="E3" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>1</v>
+      </c>
+      <c r="G3" s="1">
+        <f>SUM(D:D) + (H3*60)</f>
+        <v>187</v>
+      </c>
+      <c r="H3" s="6">
+        <f>SUM(E:E)</f>
+        <v>3</v>
+      </c>
+      <c r="I3" s="5">
+        <f>Table2[[#This Row],[Total Minutes]]/60</f>
+        <v>3.1166666666666667</v>
+      </c>
+      <c r="J3" s="1" t="str">
+        <f>IF(Table2[[#This Row],[Hour Percent]] &gt;= Table2[[#This Row],[Hours Needed]], "Hours have been met", "More hours needed")</f>
+        <v>More hours needed</v>
+      </c>
+      <c r="K3" s="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A4" s="7">
+        <v>46028</v>
+      </c>
+      <c r="B4" s="2">
+        <v>46028.611975115738</v>
+      </c>
+      <c r="C4" s="2">
+        <v>46028.69975428241</v>
+      </c>
+      <c r="D4" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>6</v>
+      </c>
+      <c r="E4" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A5" s="7">
+        <v>46029</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A6" s="7">
+        <v>46030</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="3">
         <f ca="1">NOW()</f>
-        <v>46028.612035185186</v>
-      </c>
-      <c r="H2" s="5">
+        <v>46028.699805208336</v>
+      </c>
+      <c r="H6" s="4">
         <f ca="1">NOW()</f>
-        <v>46028.612035185186</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3" s="2">
-        <v>46027</v>
-      </c>
-      <c r="B3" s="3">
-        <v>46027.625</v>
-      </c>
-      <c r="C3" s="3">
-        <v>46027.667568055556</v>
-      </c>
-      <c r="D3" s="6">
-        <f>MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]))</f>
-        <v>1</v>
-      </c>
-      <c r="E3" s="6">
-        <f>HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])</f>
-        <v>1</v>
-      </c>
-      <c r="J3" s="1" t="e">
-        <f>SUM(D:D) + (K3*60)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="K3" s="8" t="e">
-        <f>SUM(E:E)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="L3" s="7" t="e">
-        <f>Table2[[#This Row],[Total Minutes]]/60</f>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A4" s="2">
-        <v>46028</v>
-      </c>
-      <c r="B4" s="3">
-        <v>46028.611975115738</v>
-      </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="6" t="e">
-        <f>MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]))</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="E4" s="6" t="e">
-        <f>HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])</f>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A5" s="2">
-        <v>46029</v>
-      </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="6">
-        <f>MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]))</f>
-        <v>0</v>
-      </c>
-      <c r="E5" s="6">
-        <f>HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A6" s="2">
-        <v>46030</v>
-      </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="6">
-        <f>MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]))</f>
-        <v>0</v>
-      </c>
-      <c r="E6" s="6">
-        <f>HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A7" s="2">
+        <v>46028.699805208336</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A7" s="7">
         <v>46031</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="6">
-        <f>MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]))</f>
-        <v>0</v>
-      </c>
-      <c r="E7" s="6">
-        <f>HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A8" s="2">
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A8" s="7">
         <v>46032</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="6">
-        <f>MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]))</f>
-        <v>0</v>
-      </c>
-      <c r="E8" s="6">
-        <f>HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A9" s="2">
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A9" s="7">
         <v>46033</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="6">
-        <f>MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]))</f>
-        <v>0</v>
-      </c>
-      <c r="E9" s="6">
-        <f>HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A10" s="2">
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A10" s="7">
         <v>46034</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="6">
-        <f>MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]))</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="6">
-        <f>HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A11" s="2">
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A11" s="7">
         <v>46035</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="6">
-        <f>MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]))</f>
-        <v>0</v>
-      </c>
-      <c r="E11" s="6">
-        <f>HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A12" s="2">
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A12" s="7">
         <v>46036</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="6">
-        <f>MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]))</f>
-        <v>0</v>
-      </c>
-      <c r="E12" s="6">
-        <f>HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A13" s="2">
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A13" s="7">
         <v>46037</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="6">
-        <f>MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]))</f>
-        <v>0</v>
-      </c>
-      <c r="E13" s="6">
-        <f>HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A14" s="2">
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A14" s="7">
         <v>46038</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="6">
-        <f>MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]))</f>
-        <v>0</v>
-      </c>
-      <c r="E14" s="6">
-        <f>HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A15" s="2">
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A15" s="7">
         <v>46039</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="6">
-        <f>MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]))</f>
-        <v>0</v>
-      </c>
-      <c r="E15" s="6">
-        <f>HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A16" s="2">
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A16" s="7">
         <v>46040</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="6">
-        <f>MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]))</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="6">
-        <f>HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])</f>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" s="2">
+      <c r="A17" s="7">
         <v>46041</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="6">
-        <f>MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]))</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="6">
-        <f>HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])</f>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" s="2">
+      <c r="A18" s="7">
         <v>46042</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="6">
-        <f>MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]))</f>
-        <v>0</v>
-      </c>
-      <c r="E18" s="6">
-        <f>HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])</f>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E18" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" s="2">
+      <c r="A19" s="7">
         <v>46043</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="6">
-        <f>MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]))</f>
-        <v>0</v>
-      </c>
-      <c r="E19" s="6">
-        <f>HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])</f>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" s="2">
+      <c r="A20" s="7">
         <v>46044</v>
       </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="6">
-        <f>MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]))</f>
-        <v>0</v>
-      </c>
-      <c r="E20" s="6">
-        <f>HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])</f>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E20" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" s="2">
+      <c r="A21" s="7">
         <v>46045</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="6">
-        <f>MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]))</f>
-        <v>0</v>
-      </c>
-      <c r="E21" s="6">
-        <f>HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])</f>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A22" s="2">
+      <c r="A22" s="7">
         <v>46046</v>
       </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="6">
-        <f>MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]))</f>
-        <v>0</v>
-      </c>
-      <c r="E22" s="6">
-        <f>HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])</f>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E22" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A23" s="2">
+      <c r="A23" s="7">
         <v>46047</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="6">
-        <f>MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]))</f>
-        <v>0</v>
-      </c>
-      <c r="E23" s="6">
-        <f>HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])</f>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E23" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A24" s="2">
+      <c r="A24" s="7">
         <v>46048</v>
       </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="6">
-        <f>MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]))</f>
-        <v>0</v>
-      </c>
-      <c r="E24" s="6">
-        <f>HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])</f>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E24" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A25" s="2">
+      <c r="A25" s="7">
         <v>46049</v>
       </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="6">
-        <f>MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]))</f>
-        <v>0</v>
-      </c>
-      <c r="E25" s="6">
-        <f>HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])</f>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E25" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A26" s="2">
+      <c r="A26" s="7">
         <v>46050</v>
       </c>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="6">
-        <f>MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]))</f>
-        <v>0</v>
-      </c>
-      <c r="E26" s="6">
-        <f>HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])</f>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E26" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A27" s="2">
+      <c r="A27" s="7">
         <v>46051</v>
       </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="6">
-        <f>MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]))</f>
-        <v>0</v>
-      </c>
-      <c r="E27" s="6">
-        <f>HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])</f>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E27" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A28" s="2">
+      <c r="A28" s="7">
         <v>46052</v>
       </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="6">
-        <f>MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]))</f>
-        <v>0</v>
-      </c>
-      <c r="E28" s="6">
-        <f>HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])</f>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E28" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A29" s="2">
+      <c r="A29" s="7">
         <v>46053</v>
       </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="6">
-        <f>MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]))</f>
-        <v>0</v>
-      </c>
-      <c r="E29" s="6">
-        <f>HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])</f>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E29" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A30" s="2">
+      <c r="A30" s="7">
         <v>46054</v>
       </c>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="6">
-        <f>MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]))</f>
-        <v>0</v>
-      </c>
-      <c r="E30" s="6">
-        <f>HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])</f>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E30" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A31" s="2">
+      <c r="A31" s="7">
         <v>46055</v>
       </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="6">
-        <f>MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]))</f>
-        <v>0</v>
-      </c>
-      <c r="E31" s="6">
-        <f>HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])</f>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E31" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A32" s="2">
+      <c r="A32" s="7">
         <v>46056</v>
       </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="6">
-        <f>MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]))</f>
-        <v>0</v>
-      </c>
-      <c r="E32" s="6">
-        <f>HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])</f>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E32" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A33" s="2">
+      <c r="A33" s="7">
         <v>46057</v>
       </c>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="6">
-        <f>MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]))</f>
-        <v>0</v>
-      </c>
-      <c r="E33" s="6">
-        <f>HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])</f>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E33" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A34" s="2">
+      <c r="A34" s="7">
         <v>46058</v>
       </c>
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="6">
-        <f>MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]))</f>
-        <v>0</v>
-      </c>
-      <c r="E34" s="6">
-        <f>HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])</f>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E34" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A35" s="2">
+      <c r="A35" s="7">
         <v>46059</v>
       </c>
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="6">
-        <f>MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]))</f>
-        <v>0</v>
-      </c>
-      <c r="E35" s="6">
-        <f>HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])</f>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E35" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A36" s="2">
+      <c r="A36" s="7">
         <v>46060</v>
       </c>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="6">
-        <f>MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]))</f>
-        <v>0</v>
-      </c>
-      <c r="E36" s="6">
-        <f>HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])</f>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E36" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A37" s="2">
+      <c r="A37" s="7">
         <v>46061</v>
       </c>
-      <c r="B37" s="3"/>
-      <c r="C37" s="3"/>
-      <c r="D37" s="6">
-        <f>MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]))</f>
-        <v>0</v>
-      </c>
-      <c r="E37" s="6">
-        <f>HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])</f>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E37" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A38" s="2">
+      <c r="A38" s="7">
         <v>46062</v>
       </c>
-      <c r="B38" s="3"/>
-      <c r="C38" s="3"/>
-      <c r="D38" s="6">
-        <f>MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]))</f>
-        <v>0</v>
-      </c>
-      <c r="E38" s="6">
-        <f>HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])</f>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E38" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A39" s="2">
+      <c r="A39" s="7">
         <v>46063</v>
       </c>
-      <c r="B39" s="3"/>
-      <c r="C39" s="3"/>
-      <c r="D39" s="6">
-        <f>MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]))</f>
-        <v>0</v>
-      </c>
-      <c r="E39" s="6">
-        <f>HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])</f>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E39" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A40" s="2">
+      <c r="A40" s="7">
         <v>46064</v>
       </c>
-      <c r="B40" s="3"/>
-      <c r="C40" s="3"/>
-      <c r="D40" s="6">
-        <f>MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]))</f>
-        <v>0</v>
-      </c>
-      <c r="E40" s="6">
-        <f>HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])</f>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E40" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A41" s="2">
+      <c r="A41" s="7">
         <v>46065</v>
       </c>
-      <c r="B41" s="3"/>
-      <c r="C41" s="3"/>
-      <c r="D41" s="6">
-        <f>MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]))</f>
-        <v>0</v>
-      </c>
-      <c r="E41" s="6">
-        <f>HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])</f>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E41" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A42" s="2">
+      <c r="A42" s="7">
         <v>46066</v>
       </c>
-      <c r="B42" s="3"/>
-      <c r="C42" s="3"/>
-      <c r="D42" s="6">
-        <f>MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]))</f>
-        <v>0</v>
-      </c>
-      <c r="E42" s="6">
-        <f>HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])</f>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E42" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A43" s="2">
+      <c r="A43" s="7">
         <v>46067</v>
       </c>
-      <c r="B43" s="3"/>
-      <c r="C43" s="3"/>
-      <c r="D43" s="6">
-        <f>MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]))</f>
-        <v>0</v>
-      </c>
-      <c r="E43" s="6">
-        <f>HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])</f>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E43" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A44" s="2">
+      <c r="A44" s="7">
         <v>46068</v>
       </c>
-      <c r="B44" s="3"/>
-      <c r="C44" s="3"/>
-      <c r="D44" s="6">
-        <f>MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]))</f>
-        <v>0</v>
-      </c>
-      <c r="E44" s="6">
-        <f>HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])</f>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E44" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A45" s="2">
+      <c r="A45" s="7">
         <v>46069</v>
       </c>
-      <c r="B45" s="3"/>
-      <c r="C45" s="3"/>
-      <c r="D45" s="6">
-        <f>MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]))</f>
-        <v>0</v>
-      </c>
-      <c r="E45" s="6">
-        <f>HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])</f>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E45" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A46" s="2">
+      <c r="A46" s="7">
         <v>46070</v>
       </c>
-      <c r="B46" s="3"/>
-      <c r="C46" s="3"/>
-      <c r="D46" s="6">
-        <f>MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]))</f>
-        <v>0</v>
-      </c>
-      <c r="E46" s="6">
-        <f>HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])</f>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E46" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A47" s="2">
+      <c r="A47" s="7">
         <v>46071</v>
       </c>
-      <c r="B47" s="3"/>
-      <c r="C47" s="3"/>
-      <c r="D47" s="6">
-        <f>MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]))</f>
-        <v>0</v>
-      </c>
-      <c r="E47" s="6">
-        <f>HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])</f>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E47" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A48" s="2">
+      <c r="A48" s="7">
         <v>46072</v>
       </c>
-      <c r="B48" s="3"/>
-      <c r="C48" s="3"/>
-      <c r="D48" s="6">
-        <f>MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]))</f>
-        <v>0</v>
-      </c>
-      <c r="E48" s="6">
-        <f>HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])</f>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E48" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A49" s="2">
+      <c r="A49" s="7">
         <v>46073</v>
       </c>
-      <c r="B49" s="3"/>
-      <c r="C49" s="3"/>
-      <c r="D49" s="6">
-        <f>MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]))</f>
-        <v>0</v>
-      </c>
-      <c r="E49" s="6">
-        <f>HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])</f>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E49" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A50" s="2">
+      <c r="A50" s="7">
         <v>46074</v>
       </c>
-      <c r="B50" s="3"/>
-      <c r="C50" s="3"/>
-      <c r="D50" s="6">
-        <f>MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]))</f>
-        <v>0</v>
-      </c>
-      <c r="E50" s="6">
-        <f>HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])</f>
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E50" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A51" s="2">
+      <c r="A51" s="7">
         <v>46075</v>
       </c>
-      <c r="B51" s="3"/>
-      <c r="C51" s="3"/>
-      <c r="D51" s="6">
-        <f>MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]))</f>
-        <v>0</v>
-      </c>
-      <c r="E51" s="6">
-        <f>HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])</f>
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E51" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A52" s="2">
+      <c r="A52" s="7">
         <v>46076</v>
       </c>
-      <c r="B52" s="3"/>
-      <c r="C52" s="3"/>
-      <c r="D52" s="6">
-        <f>MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]))</f>
-        <v>0</v>
-      </c>
-      <c r="E52" s="6">
-        <f>HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])</f>
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E52" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A53" s="2">
+      <c r="A53" s="7">
         <v>46077</v>
       </c>
-      <c r="B53" s="3"/>
-      <c r="C53" s="3"/>
-      <c r="D53" s="6">
-        <f>MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]))</f>
-        <v>0</v>
-      </c>
-      <c r="E53" s="6">
-        <f>HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])</f>
+      <c r="B53" s="2"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E53" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A54" s="2">
+      <c r="A54" s="7">
         <v>46078</v>
       </c>
-      <c r="B54" s="3"/>
-      <c r="C54" s="3"/>
-      <c r="D54" s="6">
-        <f>MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]))</f>
-        <v>0</v>
-      </c>
-      <c r="E54" s="6">
-        <f>HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])</f>
+      <c r="B54" s="2"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E54" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A55" s="2">
+      <c r="A55" s="7">
         <v>46079</v>
       </c>
-      <c r="B55" s="3"/>
-      <c r="C55" s="3"/>
-      <c r="D55" s="6">
-        <f>MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]))</f>
-        <v>0</v>
-      </c>
-      <c r="E55" s="6">
-        <f>HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])</f>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E55" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A56" s="2">
+      <c r="A56" s="7">
         <v>46080</v>
       </c>
-      <c r="B56" s="3"/>
-      <c r="C56" s="3"/>
-      <c r="D56" s="6">
-        <f>MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]))</f>
-        <v>0</v>
-      </c>
-      <c r="E56" s="6">
-        <f>HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])</f>
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E56" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A57" s="2">
+      <c r="A57" s="7">
         <v>46081</v>
       </c>
-      <c r="B57" s="3"/>
-      <c r="C57" s="3"/>
-      <c r="D57" s="6">
-        <f>MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]))</f>
-        <v>0</v>
-      </c>
-      <c r="E57" s="6">
-        <f>HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])</f>
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E57" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A58" s="7">
+        <v>46082</v>
+      </c>
+      <c r="B58" s="2"/>
+      <c r="C58" s="2"/>
+      <c r="D58" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E58" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A59" s="7">
+        <v>46083</v>
+      </c>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E59" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A60" s="7">
+        <v>46084</v>
+      </c>
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E60" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A61" s="7">
+        <v>46085</v>
+      </c>
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E61" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A62" s="7">
+        <v>46086</v>
+      </c>
+      <c r="B62" s="2"/>
+      <c r="C62" s="2"/>
+      <c r="D62" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E62" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A63" s="7">
+        <v>46087</v>
+      </c>
+      <c r="B63" s="2"/>
+      <c r="C63" s="2"/>
+      <c r="D63" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E63" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A64" s="7">
+        <v>46088</v>
+      </c>
+      <c r="B64" s="2"/>
+      <c r="C64" s="2"/>
+      <c r="D64" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E64" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A65" s="7">
+        <v>46089</v>
+      </c>
+      <c r="B65" s="2"/>
+      <c r="C65" s="2"/>
+      <c r="D65" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E65" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A66" s="7">
+        <v>46090</v>
+      </c>
+      <c r="B66" s="2"/>
+      <c r="C66" s="2"/>
+      <c r="D66" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E66" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A67" s="7">
+        <v>46091</v>
+      </c>
+      <c r="B67" s="2"/>
+      <c r="C67" s="2"/>
+      <c r="D67" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E67" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A68" s="7">
+        <v>46092</v>
+      </c>
+      <c r="B68" s="2"/>
+      <c r="C68" s="2"/>
+      <c r="D68" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E68" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A69" s="7">
+        <v>46093</v>
+      </c>
+      <c r="B69" s="2"/>
+      <c r="C69" s="2"/>
+      <c r="D69" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E69" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A70" s="7">
+        <v>46094</v>
+      </c>
+      <c r="B70" s="2"/>
+      <c r="C70" s="2"/>
+      <c r="D70" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E70" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A71" s="7">
+        <v>46095</v>
+      </c>
+      <c r="B71" s="2"/>
+      <c r="C71" s="2"/>
+      <c r="D71" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E71" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A72" s="7">
+        <v>46096</v>
+      </c>
+      <c r="B72" s="2"/>
+      <c r="C72" s="2"/>
+      <c r="D72" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E72" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A73" s="7">
+        <v>46097</v>
+      </c>
+      <c r="B73" s="2"/>
+      <c r="C73" s="2"/>
+      <c r="D73" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E73" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A74" s="7">
+        <v>46098</v>
+      </c>
+      <c r="B74" s="2"/>
+      <c r="C74" s="2"/>
+      <c r="D74" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E74" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A75" s="7">
+        <v>46099</v>
+      </c>
+      <c r="B75" s="2"/>
+      <c r="C75" s="2"/>
+      <c r="D75" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E75" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="J1:L1"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="G1:K1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Baseline_docs/Time Sheet.xlsx
+++ b/Baseline_docs/Time Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wskinner\On Drive Files\Git\Secure-Multi-Layer-Network-Project---Capstone\Baseline_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{293FBC09-3151-4D34-BEB6-C74A6AEC540B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3227279-8B07-470D-AC25-4585521B773D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Day</t>
   </si>
@@ -72,6 +72,9 @@
   </si>
   <si>
     <t>Hours Met</t>
+  </si>
+  <si>
+    <t>Extra Mins</t>
   </si>
 </sst>
 </file>
@@ -146,7 +149,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="14">
+  <dxfs count="15">
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -168,6 +171,10 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -210,12 +217,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AECFD94D-BC69-43FE-8A1B-A8548D9C1CB8}" name="Table1" displayName="Table1" ref="A2:E75" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
-  <autoFilter ref="A2:E75" xr:uid="{AECFD94D-BC69-43FE-8A1B-A8548D9C1CB8}"/>
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{7D80F612-B207-4202-A1B2-4CDD0B31BE04}" name="Day" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{809082CE-E596-42B5-B407-A4E321ECCB56}" name="Start" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{387E5ED8-33C5-4EC7-A1F3-CE1B1DDAF190}" name="Stop" dataDxfId="9"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AECFD94D-BC69-43FE-8A1B-A8548D9C1CB8}" name="Table1" displayName="Table1" ref="A2:F75" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13">
+  <autoFilter ref="A2:F75" xr:uid="{AECFD94D-BC69-43FE-8A1B-A8548D9C1CB8}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{7D80F612-B207-4202-A1B2-4CDD0B31BE04}" name="Day" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{809082CE-E596-42B5-B407-A4E321ECCB56}" name="Start" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{387E5ED8-33C5-4EC7-A1F3-CE1B1DDAF190}" name="Stop" dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{F560E705-D838-45AE-BE0C-270C69667AC2}" name="Extra Mins" dataDxfId="9"/>
     <tableColumn id="4" xr3:uid="{A72F3DB0-D92C-4679-A812-253243311EF0}" name="Minutes " dataDxfId="8">
       <calculatedColumnFormula>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</calculatedColumnFormula>
     </tableColumn>
@@ -228,14 +236,14 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{BCDE2B7C-F4D9-498C-BDF8-E77B124E5F78}" name="Table2" displayName="Table2" ref="G2:K3" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
-  <autoFilter ref="G2:K3" xr:uid="{BCDE2B7C-F4D9-498C-BDF8-E77B124E5F78}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{BCDE2B7C-F4D9-498C-BDF8-E77B124E5F78}" name="Table2" displayName="Table2" ref="H2:L3" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+  <autoFilter ref="H2:L3" xr:uid="{BCDE2B7C-F4D9-498C-BDF8-E77B124E5F78}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{25609316-2FC7-4598-9816-D773B5ABDED5}" name="Total Minutes" dataDxfId="4">
-      <calculatedColumnFormula>SUM(D:D) + (H3*60)</calculatedColumnFormula>
+      <calculatedColumnFormula>SUM(E:E) + (I3*60) + SUM(D:D)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{C48BBBC8-9BDB-469A-A714-B3361A5491E0}" name="Total Hours" dataDxfId="3">
-      <calculatedColumnFormula>SUM(E:E)</calculatedColumnFormula>
+      <calculatedColumnFormula>SUM(F:F)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{B3EDE8C1-FEE6-4401-BAF1-7A6A74F4FE86}" name="Hour Percent" dataDxfId="2">
       <calculatedColumnFormula>Table2[[#This Row],[Total Minutes]]/60</calculatedColumnFormula>
@@ -512,23 +520,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K75"/>
-  <sheetFormatPr defaultColWidth="16" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:L75"/>
+  <sheetFormatPr defaultColWidth="13.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.36328125" style="1" customWidth="1"/>
-    <col min="2" max="3" width="16" style="1"/>
-    <col min="4" max="4" width="11.54296875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.54296875" style="5" customWidth="1"/>
-    <col min="6" max="6" width="3.7265625" style="1" customWidth="1"/>
-    <col min="7" max="9" width="16" style="1"/>
-    <col min="10" max="10" width="22.90625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="17.26953125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="16" style="1"/>
-    <col min="13" max="13" width="22.08984375" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="16" style="1"/>
+    <col min="1" max="3" width="13.81640625" style="1"/>
+    <col min="4" max="5" width="13.81640625" style="5"/>
+    <col min="6" max="6" width="13.81640625" style="1"/>
+    <col min="7" max="7" width="2.7265625" style="1" customWidth="1"/>
+    <col min="8" max="10" width="16.54296875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="17.36328125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="16.54296875" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="13.81640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
         <v>3</v>
       </c>
@@ -536,6 +541,7 @@
       <c r="C1" s="8"/>
       <c r="D1" s="8"/>
       <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
       <c r="G1" s="8" t="s">
         <v>5</v>
       </c>
@@ -544,7 +550,7 @@
       <c r="J1" s="8"/>
       <c r="K1" s="8"/>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -554,29 +560,32 @@
       <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="F2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="7">
         <v>46027</v>
       </c>
@@ -586,35 +595,35 @@
       <c r="C3" s="2">
         <v>46027.667568055556</v>
       </c>
-      <c r="D3" s="5">
+      <c r="E3" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
         <v>1</v>
       </c>
-      <c r="E3" s="5">
+      <c r="F3" s="5">
         <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
         <v>1</v>
       </c>
-      <c r="G3" s="1">
-        <f>SUM(D:D) + (H3*60)</f>
-        <v>187</v>
-      </c>
-      <c r="H3" s="6">
-        <f>SUM(E:E)</f>
-        <v>3</v>
-      </c>
-      <c r="I3" s="5">
+      <c r="H3" s="1">
+        <f>SUM(E:E) + (I3*60) + SUM(D:D)</f>
+        <v>387</v>
+      </c>
+      <c r="I3" s="6">
+        <f>SUM(F:F)</f>
+        <v>6</v>
+      </c>
+      <c r="J3" s="5">
         <f>Table2[[#This Row],[Total Minutes]]/60</f>
-        <v>3.1166666666666667</v>
-      </c>
-      <c r="J3" s="1" t="str">
+        <v>6.45</v>
+      </c>
+      <c r="K3" s="1" t="str">
         <f>IF(Table2[[#This Row],[Hour Percent]] &gt;= Table2[[#This Row],[Hours Needed]], "Hours have been met", "More hours needed")</f>
         <v>More hours needed</v>
       </c>
-      <c r="K3" s="1">
+      <c r="L3" s="1">
         <v>200</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="7">
         <v>46028</v>
       </c>
@@ -624,1092 +633,1096 @@
       <c r="C4" s="2">
         <v>46028.69975428241</v>
       </c>
-      <c r="D4" s="5">
+      <c r="E4" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
         <v>6</v>
       </c>
-      <c r="E4" s="5">
+      <c r="F4" s="5">
         <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" s="7">
         <v>46029</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
+      <c r="B5" s="2">
+        <v>46029.55702847222</v>
+      </c>
+      <c r="C5" s="2">
+        <v>46029.69652002315</v>
       </c>
       <c r="E5" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>20</v>
+      </c>
+      <c r="F5" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="7">
         <v>46030</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
-      <c r="D6" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E6" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-      <c r="G6" s="3">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="3">
         <f ca="1">NOW()</f>
-        <v>46028.699805208336</v>
-      </c>
-      <c r="H6" s="4">
+        <v>46029.696520486112</v>
+      </c>
+      <c r="I6" s="4">
         <f ca="1">NOW()</f>
-        <v>46028.699805208336</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+        <v>46029.696520486112</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="7">
         <v>46031</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
-      <c r="D7" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E7" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="7">
         <v>46032</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
-      <c r="D8" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E8" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" s="7">
         <v>46033</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
-      <c r="D9" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E9" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" s="7">
         <v>46034</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
-      <c r="D10" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E10" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" s="7">
         <v>46035</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
-      <c r="D11" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E11" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="7">
         <v>46036</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
-      <c r="D12" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E12" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="7">
         <v>46037</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
-      <c r="D13" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E13" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" s="7">
         <v>46038</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
-      <c r="D14" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E14" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" s="7">
         <v>46039</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
-      <c r="D15" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E15" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" s="7">
         <v>46040</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
-      <c r="D16" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E16" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="7">
         <v>46041</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
-      <c r="D17" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E17" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="7">
         <v>46042</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
-      <c r="D18" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E18" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F18" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="7">
         <v>46043</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
-      <c r="D19" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E19" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F19" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="7">
         <v>46044</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
-      <c r="D20" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E20" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F20" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="7">
         <v>46045</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
-      <c r="D21" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E21" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="7">
         <v>46046</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
-      <c r="D22" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E22" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F22" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="7">
         <v>46047</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
-      <c r="D23" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E23" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F23" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="7">
         <v>46048</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
-      <c r="D24" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E24" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F24" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="7">
         <v>46049</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
-      <c r="D25" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E25" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F25" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="7">
         <v>46050</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
-      <c r="D26" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E26" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F26" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="7">
         <v>46051</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
-      <c r="D27" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E27" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F27" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="7">
         <v>46052</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
-      <c r="D28" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E28" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F28" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="7">
         <v>46053</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
-      <c r="D29" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E29" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F29" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="7">
         <v>46054</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
-      <c r="D30" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E30" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F30" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="7">
         <v>46055</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
-      <c r="D31" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E31" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F31" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="7">
         <v>46056</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
-      <c r="D32" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E32" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F32" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="7">
         <v>46057</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
-      <c r="D33" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E33" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F33" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="7">
         <v>46058</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
-      <c r="D34" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E34" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F34" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="7">
         <v>46059</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
-      <c r="D35" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E35" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F35" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="7">
         <v>46060</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
-      <c r="D36" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E36" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F36" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="7">
         <v>46061</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
-      <c r="D37" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E37" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F37" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="7">
         <v>46062</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
-      <c r="D38" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E38" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F38" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="7">
         <v>46063</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
-      <c r="D39" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E39" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F39" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="7">
         <v>46064</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
-      <c r="D40" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E40" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F40" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="7">
         <v>46065</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
-      <c r="D41" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E41" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F41" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="7">
         <v>46066</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
-      <c r="D42" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E42" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F42" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="7">
         <v>46067</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
-      <c r="D43" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E43" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F43" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="7">
         <v>46068</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
-      <c r="D44" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E44" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F44" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" s="7">
         <v>46069</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
-      <c r="D45" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E45" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F45" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" s="7">
         <v>46070</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
-      <c r="D46" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E46" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F46" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" s="7">
         <v>46071</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
-      <c r="D47" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E47" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F47" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" s="7">
         <v>46072</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
-      <c r="D48" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E48" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F48" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" s="7">
         <v>46073</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
-      <c r="D49" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E49" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F49" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="7">
         <v>46074</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
-      <c r="D50" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E50" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F50" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="7">
         <v>46075</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
-      <c r="D51" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E51" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F51" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="7">
         <v>46076</v>
       </c>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
-      <c r="D52" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E52" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F52" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" s="7">
         <v>46077</v>
       </c>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
-      <c r="D53" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E53" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F53" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" s="7">
         <v>46078</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
-      <c r="D54" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E54" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F54" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" s="7">
         <v>46079</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
-      <c r="D55" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E55" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F55" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" s="7">
         <v>46080</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
-      <c r="D56" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E56" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F56" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" s="7">
         <v>46081</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
-      <c r="D57" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E57" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F57" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" s="7">
         <v>46082</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
-      <c r="D58" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E58" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F58" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="7">
         <v>46083</v>
       </c>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
-      <c r="D59" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E59" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F59" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" s="7">
         <v>46084</v>
       </c>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
-      <c r="D60" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E60" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F60" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" s="7">
         <v>46085</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
-      <c r="D61" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E61" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F61" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" s="7">
         <v>46086</v>
       </c>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
-      <c r="D62" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E62" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F62" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" s="7">
         <v>46087</v>
       </c>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
-      <c r="D63" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E63" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F63" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" s="7">
         <v>46088</v>
       </c>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
-      <c r="D64" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E64" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F64" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" s="7">
         <v>46089</v>
       </c>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
-      <c r="D65" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E65" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F65" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" s="7">
         <v>46090</v>
       </c>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
-      <c r="D66" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E66" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F66" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" s="7">
         <v>46091</v>
       </c>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
-      <c r="D67" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E67" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F67" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" s="7">
         <v>46092</v>
       </c>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
-      <c r="D68" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E68" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F68" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" s="7">
         <v>46093</v>
       </c>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
-      <c r="D69" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E69" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F69" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" s="7">
         <v>46094</v>
       </c>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
-      <c r="D70" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E70" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F70" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" s="7">
         <v>46095</v>
       </c>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
-      <c r="D71" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E71" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F71" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" s="7">
         <v>46096</v>
       </c>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
-      <c r="D72" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E72" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F72" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" s="7">
         <v>46097</v>
       </c>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
-      <c r="D73" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E73" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F73" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" s="7">
         <v>46098</v>
       </c>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
-      <c r="D74" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E74" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F74" s="5">
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75" s="7">
         <v>46099</v>
       </c>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
-      <c r="D75" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
       <c r="E75" s="5">
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F75" s="5">
         <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:E1"/>
     <mergeCell ref="G1:K1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Baseline_docs/Time Sheet.xlsx
+++ b/Baseline_docs/Time Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wskinner\On Drive Files\Git\Secure-Multi-Layer-Network-Project---Capstone\Baseline_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3227279-8B07-470D-AC25-4585521B773D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81938C1A-4946-47A2-A8CA-73F13E82F5A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -665,7 +665,9 @@
       <c r="A6" s="7">
         <v>46030</v>
       </c>
-      <c r="B6" s="2"/>
+      <c r="B6" s="2">
+        <v>46030.619527314811</v>
+      </c>
       <c r="C6" s="2"/>
       <c r="E6" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
@@ -677,11 +679,11 @@
       </c>
       <c r="H6" s="3">
         <f ca="1">NOW()</f>
-        <v>46029.696520486112</v>
+        <v>46030.61960150463</v>
       </c>
       <c r="I6" s="4">
         <f ca="1">NOW()</f>
-        <v>46029.696520486112</v>
+        <v>46030.61960150463</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">

--- a/Baseline_docs/Time Sheet.xlsx
+++ b/Baseline_docs/Time Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wskinner\On Drive Files\Git\Secure-Multi-Layer-Network-Project---Capstone\Baseline_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81938C1A-4946-47A2-A8CA-73F13E82F5A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C1E1184-8EC5-4407-A42B-84F091454981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -605,15 +605,15 @@
       </c>
       <c r="H3" s="1">
         <f>SUM(E:E) + (I3*60) + SUM(D:D)</f>
-        <v>387</v>
+        <v>472</v>
       </c>
       <c r="I3" s="6">
         <f>SUM(F:F)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J3" s="5">
         <f>Table2[[#This Row],[Total Minutes]]/60</f>
-        <v>6.45</v>
+        <v>7.8666666666666663</v>
       </c>
       <c r="K3" s="1" t="str">
         <f>IF(Table2[[#This Row],[Hour Percent]] &gt;= Table2[[#This Row],[Hours Needed]], "Hours have been met", "More hours needed")</f>
@@ -668,22 +668,24 @@
       <c r="B6" s="2">
         <v>46030.619527314811</v>
       </c>
-      <c r="C6" s="2"/>
+      <c r="C6" s="2">
+        <v>46030.678883217595</v>
+      </c>
       <c r="E6" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F6" s="5">
         <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" s="3">
         <f ca="1">NOW()</f>
-        <v>46030.61960150463</v>
+        <v>46030.678955439813</v>
       </c>
       <c r="I6" s="4">
         <f ca="1">NOW()</f>
-        <v>46030.61960150463</v>
+        <v>46030.678955439813</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">

--- a/Baseline_docs/Time Sheet.xlsx
+++ b/Baseline_docs/Time Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wskinner\On Drive Files\Git\Secure-Multi-Layer-Network-Project---Capstone\Baseline_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C1E1184-8EC5-4407-A42B-84F091454981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{433528D9-1139-4695-A59A-B04A46B7EAF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
   <si>
     <t>Day</t>
   </si>
@@ -75,6 +75,9 @@
   </si>
   <si>
     <t>Extra Mins</t>
+  </si>
+  <si>
+    <t>none</t>
   </si>
 </sst>
 </file>
@@ -605,15 +608,15 @@
       </c>
       <c r="H3" s="1">
         <f>SUM(E:E) + (I3*60) + SUM(D:D)</f>
-        <v>472</v>
+        <v>606</v>
       </c>
       <c r="I3" s="6">
         <f>SUM(F:F)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J3" s="5">
         <f>Table2[[#This Row],[Total Minutes]]/60</f>
-        <v>7.8666666666666663</v>
+        <v>10.1</v>
       </c>
       <c r="K3" s="1" t="str">
         <f>IF(Table2[[#This Row],[Hour Percent]] &gt;= Table2[[#This Row],[Hours Needed]], "Hours have been met", "More hours needed")</f>
@@ -652,6 +655,9 @@
       <c r="C5" s="2">
         <v>46029.69652002315</v>
       </c>
+      <c r="D5" s="5">
+        <v>5</v>
+      </c>
       <c r="E5" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
         <v>20</v>
@@ -681,34 +687,42 @@
       </c>
       <c r="H6" s="3">
         <f ca="1">NOW()</f>
-        <v>46030.678955439813</v>
+        <v>46031.62400787037</v>
       </c>
       <c r="I6" s="4">
         <f ca="1">NOW()</f>
-        <v>46030.678955439813</v>
+        <v>46031.62400787037</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="7">
         <v>46031</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
+      <c r="B7" s="2">
+        <v>46031.535747222224</v>
+      </c>
+      <c r="C7" s="2">
+        <v>46031.625451388885</v>
+      </c>
       <c r="E7" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F7" s="5">
         <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="7">
         <v>46032</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
+      <c r="B8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="E8" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
         <v>0</v>
@@ -722,8 +736,12 @@
       <c r="A9" s="7">
         <v>46033</v>
       </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
+      <c r="B9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="E9" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
         <v>0</v>

--- a/Baseline_docs/Time Sheet.xlsx
+++ b/Baseline_docs/Time Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wskinner\On Drive Files\Git\Secure-Multi-Layer-Network-Project---Capstone\Baseline_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{433528D9-1139-4695-A59A-B04A46B7EAF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6306BF0E-2124-45C2-879D-22E4D4B6CE99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -687,11 +687,11 @@
       </c>
       <c r="H6" s="3">
         <f ca="1">NOW()</f>
-        <v>46031.62400787037</v>
+        <v>46034.488701273149</v>
       </c>
       <c r="I6" s="4">
         <f ca="1">NOW()</f>
-        <v>46031.62400787037</v>
+        <v>46034.488701273149</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
@@ -755,7 +755,9 @@
       <c r="A10" s="7">
         <v>46034</v>
       </c>
-      <c r="B10" s="2"/>
+      <c r="B10" s="2">
+        <v>46034.488603819445</v>
+      </c>
       <c r="C10" s="2"/>
       <c r="E10" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>

--- a/Baseline_docs/Time Sheet.xlsx
+++ b/Baseline_docs/Time Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wskinner\On Drive Files\Git\Secure-Multi-Layer-Network-Project---Capstone\Baseline_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6306BF0E-2124-45C2-879D-22E4D4B6CE99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBD131E3-3849-4EEF-96B2-D69AF7FB23A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -608,15 +608,15 @@
       </c>
       <c r="H3" s="1">
         <f>SUM(E:E) + (I3*60) + SUM(D:D)</f>
-        <v>606</v>
+        <v>870</v>
       </c>
       <c r="I3" s="6">
         <f>SUM(F:F)</f>
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J3" s="5">
         <f>Table2[[#This Row],[Total Minutes]]/60</f>
-        <v>10.1</v>
+        <v>14.5</v>
       </c>
       <c r="K3" s="1" t="str">
         <f>IF(Table2[[#This Row],[Hour Percent]] &gt;= Table2[[#This Row],[Hours Needed]], "Hours have been met", "More hours needed")</f>
@@ -687,11 +687,11 @@
       </c>
       <c r="H6" s="3">
         <f ca="1">NOW()</f>
-        <v>46034.488701273149</v>
+        <v>46034.672508217591</v>
       </c>
       <c r="I6" s="4">
         <f ca="1">NOW()</f>
-        <v>46034.488701273149</v>
+        <v>46034.672508217591</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
@@ -758,14 +758,16 @@
       <c r="B10" s="2">
         <v>46034.488603819445</v>
       </c>
-      <c r="C10" s="2"/>
+      <c r="C10" s="2">
+        <v>46034.672431481478</v>
+      </c>
       <c r="E10" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F10" s="5">
         <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">

--- a/Baseline_docs/Time Sheet.xlsx
+++ b/Baseline_docs/Time Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wskinner\On Drive Files\Git\Secure-Multi-Layer-Network-Project---Capstone\Baseline_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBD131E3-3849-4EEF-96B2-D69AF7FB23A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFE8BE5C-2D9B-4C28-8BD2-2D0B23E0D2BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -608,15 +608,15 @@
       </c>
       <c r="H3" s="1">
         <f>SUM(E:E) + (I3*60) + SUM(D:D)</f>
-        <v>870</v>
+        <v>1137</v>
       </c>
       <c r="I3" s="6">
         <f>SUM(F:F)</f>
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J3" s="5">
         <f>Table2[[#This Row],[Total Minutes]]/60</f>
-        <v>14.5</v>
+        <v>18.95</v>
       </c>
       <c r="K3" s="1" t="str">
         <f>IF(Table2[[#This Row],[Hour Percent]] &gt;= Table2[[#This Row],[Hours Needed]], "Hours have been met", "More hours needed")</f>
@@ -687,11 +687,11 @@
       </c>
       <c r="H6" s="3">
         <f ca="1">NOW()</f>
-        <v>46034.672508217591</v>
+        <v>46035.564942245372</v>
       </c>
       <c r="I6" s="4">
         <f ca="1">NOW()</f>
-        <v>46034.672508217591</v>
+        <v>46035.564942245372</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
@@ -774,15 +774,19 @@
       <c r="A11" s="7">
         <v>46035</v>
       </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
+      <c r="B11" s="2">
+        <v>46035.564696643516</v>
+      </c>
+      <c r="C11" s="2">
+        <v>46035.750115740739</v>
+      </c>
       <c r="E11" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F11" s="5">
         <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">

--- a/Baseline_docs/Time Sheet.xlsx
+++ b/Baseline_docs/Time Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wskinner\On Drive Files\Git\Secure-Multi-Layer-Network-Project---Capstone\Baseline_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFE8BE5C-2D9B-4C28-8BD2-2D0B23E0D2BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88A1BAD5-6FFC-494E-83D5-15FE3F38638E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -608,15 +608,15 @@
       </c>
       <c r="H3" s="1">
         <f>SUM(E:E) + (I3*60) + SUM(D:D)</f>
-        <v>1137</v>
+        <v>1308</v>
       </c>
       <c r="I3" s="6">
         <f>SUM(F:F)</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J3" s="5">
         <f>Table2[[#This Row],[Total Minutes]]/60</f>
-        <v>18.95</v>
+        <v>21.8</v>
       </c>
       <c r="K3" s="1" t="str">
         <f>IF(Table2[[#This Row],[Hour Percent]] &gt;= Table2[[#This Row],[Hours Needed]], "Hours have been met", "More hours needed")</f>
@@ -687,11 +687,11 @@
       </c>
       <c r="H6" s="3">
         <f ca="1">NOW()</f>
-        <v>46035.564942245372</v>
+        <v>46036.612314467595</v>
       </c>
       <c r="I6" s="4">
         <f ca="1">NOW()</f>
-        <v>46035.564942245372</v>
+        <v>46036.612314467595</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
@@ -793,15 +793,19 @@
       <c r="A12" s="7">
         <v>46036</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
+      <c r="B12" s="2">
+        <v>46036.506007870368</v>
+      </c>
+      <c r="C12" s="2">
+        <v>46036.625069444446</v>
+      </c>
       <c r="E12" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="F12" s="5">
         <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">

--- a/Baseline_docs/Time Sheet.xlsx
+++ b/Baseline_docs/Time Sheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wskinner\On Drive Files\Git\Secure-Multi-Layer-Network-Project---Capstone\Baseline_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88A1BAD5-6FFC-494E-83D5-15FE3F38638E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEE8CFDE-EA3E-4B20-8276-93FE35141603}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
   <si>
     <t>Day</t>
   </si>
@@ -78,6 +78,15 @@
   </si>
   <si>
     <t>none</t>
+  </si>
+  <si>
+    <t>Weeks</t>
+  </si>
+  <si>
+    <t>Minutes</t>
+  </si>
+  <si>
+    <t>Hour %</t>
   </si>
 </sst>
 </file>
@@ -152,7 +161,28 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="21">
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -220,17 +250,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AECFD94D-BC69-43FE-8A1B-A8548D9C1CB8}" name="Table1" displayName="Table1" ref="A2:F75" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AECFD94D-BC69-43FE-8A1B-A8548D9C1CB8}" name="Table1" displayName="Table1" ref="A2:F75" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
   <autoFilter ref="A2:F75" xr:uid="{AECFD94D-BC69-43FE-8A1B-A8548D9C1CB8}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{7D80F612-B207-4202-A1B2-4CDD0B31BE04}" name="Day" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{809082CE-E596-42B5-B407-A4E321ECCB56}" name="Start" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{387E5ED8-33C5-4EC7-A1F3-CE1B1DDAF190}" name="Stop" dataDxfId="10"/>
-    <tableColumn id="6" xr3:uid="{F560E705-D838-45AE-BE0C-270C69667AC2}" name="Extra Mins" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{A72F3DB0-D92C-4679-A812-253243311EF0}" name="Minutes " dataDxfId="8">
+    <tableColumn id="1" xr3:uid="{7D80F612-B207-4202-A1B2-4CDD0B31BE04}" name="Day" dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{809082CE-E596-42B5-B407-A4E321ECCB56}" name="Start" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{387E5ED8-33C5-4EC7-A1F3-CE1B1DDAF190}" name="Stop" dataDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{F560E705-D838-45AE-BE0C-270C69667AC2}" name="Extra Mins" dataDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{A72F3DB0-D92C-4679-A812-253243311EF0}" name="Minutes " dataDxfId="14">
       <calculatedColumnFormula>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{CE4B143E-B608-48C4-8FCC-14B01E692DCB}" name="Hours" dataDxfId="7">
+    <tableColumn id="5" xr3:uid="{CE4B143E-B608-48C4-8FCC-14B01E692DCB}" name="Hours" dataDxfId="13">
       <calculatedColumnFormula>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -239,24 +269,39 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{BCDE2B7C-F4D9-498C-BDF8-E77B124E5F78}" name="Table2" displayName="Table2" ref="H2:L3" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{BCDE2B7C-F4D9-498C-BDF8-E77B124E5F78}" name="Table2" displayName="Table2" ref="H2:L3" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
   <autoFilter ref="H2:L3" xr:uid="{BCDE2B7C-F4D9-498C-BDF8-E77B124E5F78}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{25609316-2FC7-4598-9816-D773B5ABDED5}" name="Total Minutes" dataDxfId="4">
+    <tableColumn id="1" xr3:uid="{25609316-2FC7-4598-9816-D773B5ABDED5}" name="Total Minutes" dataDxfId="10">
       <calculatedColumnFormula>SUM(E:E) + (I3*60) + SUM(D:D)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C48BBBC8-9BDB-469A-A714-B3361A5491E0}" name="Total Hours" dataDxfId="3">
+    <tableColumn id="2" xr3:uid="{C48BBBC8-9BDB-469A-A714-B3361A5491E0}" name="Total Hours" dataDxfId="9">
       <calculatedColumnFormula>SUM(F:F)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{B3EDE8C1-FEE6-4401-BAF1-7A6A74F4FE86}" name="Hour Percent" dataDxfId="2">
+    <tableColumn id="3" xr3:uid="{B3EDE8C1-FEE6-4401-BAF1-7A6A74F4FE86}" name="Hour Percent" dataDxfId="8">
       <calculatedColumnFormula>Table2[[#This Row],[Total Minutes]]/60</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{8FB2D23B-72D8-4504-BE1A-A47C565D5166}" name="Hours Met" dataDxfId="1">
+    <tableColumn id="4" xr3:uid="{8FB2D23B-72D8-4504-BE1A-A47C565D5166}" name="Hours Met" dataDxfId="7">
       <calculatedColumnFormula>IF(Table2[[#This Row],[Hour Percent]] &gt;= Table2[[#This Row],[Hours Needed]], "Hours have been met", "More hours needed")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{643AEBD5-F2A2-4877-923F-2A6F10830FA5}" name="Hours Needed" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{643AEBD5-F2A2-4877-923F-2A6F10830FA5}" name="Hours Needed" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{0B533ACD-D878-47CD-A04A-12CDF739F4F4}" name="Table3" displayName="Table3" ref="N2:Q12" totalsRowShown="0" headerRowDxfId="4" dataDxfId="5">
+  <autoFilter ref="N2:Q12" xr:uid="{0B533ACD-D878-47CD-A04A-12CDF739F4F4}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{CFA6B21D-D050-4C14-8F9A-5D7117BEA113}" name="Weeks" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{1CA91632-7336-422D-ABF9-C5E3F08EFBA5}" name="Minutes" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{BB9EBBBA-CBEE-4ACF-8769-1D581F89C8FE}" name="Hours" dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{8911D862-F455-4BFD-BDFF-6839D678C8CE}" name="Hour %" dataDxfId="1">
+      <calculatedColumnFormula>O3/60</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="1" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -523,7 +568,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L75"/>
+  <dimension ref="A1:Q75"/>
   <sheetFormatPr defaultColWidth="13.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="3" width="13.81640625" style="1"/>
@@ -533,10 +578,11 @@
     <col min="8" max="10" width="16.54296875" style="1" customWidth="1"/>
     <col min="11" max="11" width="17.36328125" style="1" customWidth="1"/>
     <col min="12" max="12" width="16.54296875" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="13.81640625" style="1"/>
+    <col min="13" max="13" width="2.81640625" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="13.81640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
         <v>3</v>
       </c>
@@ -553,7 +599,7 @@
       <c r="J1" s="8"/>
       <c r="K1" s="8"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -587,8 +633,20 @@
       <c r="L2" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3" s="7">
         <v>46027</v>
       </c>
@@ -608,25 +666,40 @@
       </c>
       <c r="H3" s="1">
         <f>SUM(E:E) + (I3*60) + SUM(D:D)</f>
-        <v>1308</v>
+        <v>1579</v>
       </c>
       <c r="I3" s="6">
         <f>SUM(F:F)</f>
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J3" s="5">
         <f>Table2[[#This Row],[Total Minutes]]/60</f>
-        <v>21.8</v>
+        <v>26.316666666666666</v>
       </c>
       <c r="K3" s="1" t="str">
         <f>IF(Table2[[#This Row],[Hour Percent]] &gt;= Table2[[#This Row],[Hours Needed]], "Hours have been met", "More hours needed")</f>
         <v>More hours needed</v>
       </c>
       <c r="L3" s="1">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+        <v>40</v>
+      </c>
+      <c r="N3" s="1">
+        <v>1</v>
+      </c>
+      <c r="O3" s="6">
+        <f>SUM(E3:E9) + (60*P3)</f>
+        <v>601</v>
+      </c>
+      <c r="P3" s="6">
+        <f>SUM(F3:F9)</f>
+        <v>9</v>
+      </c>
+      <c r="Q3" s="5">
+        <f>O3/60</f>
+        <v>10.016666666666667</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4" s="7">
         <v>46028</v>
       </c>
@@ -644,8 +717,23 @@
         <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N4" s="1">
+        <v>2</v>
+      </c>
+      <c r="O4" s="6">
+        <f>SUM(E10:E16) + (60*P4)</f>
+        <v>973</v>
+      </c>
+      <c r="P4" s="6">
+        <f>SUM(F10:F16)</f>
+        <v>14</v>
+      </c>
+      <c r="Q4" s="5">
+        <f>O4/60</f>
+        <v>16.216666666666665</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5" s="7">
         <v>46029</v>
       </c>
@@ -666,8 +754,23 @@
         <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N5" s="1">
+        <v>3</v>
+      </c>
+      <c r="O5" s="6">
+        <f>SUM(E17:E23) + (60*P5)</f>
+        <v>0</v>
+      </c>
+      <c r="P5" s="6">
+        <f>SUM(F17:F23)</f>
+        <v>0</v>
+      </c>
+      <c r="Q5" s="5">
+        <f t="shared" ref="Q5:Q12" si="0">O5/60</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6" s="7">
         <v>46030</v>
       </c>
@@ -687,14 +790,23 @@
       </c>
       <c r="H6" s="3">
         <f ca="1">NOW()</f>
-        <v>46036.612314467595</v>
+        <v>46037.670982291667</v>
       </c>
       <c r="I6" s="4">
         <f ca="1">NOW()</f>
-        <v>46036.612314467595</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+        <v>46037.670982291667</v>
+      </c>
+      <c r="N6" s="1">
+        <v>4</v>
+      </c>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6"/>
+      <c r="Q6" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7" s="7">
         <v>46031</v>
       </c>
@@ -712,8 +824,17 @@
         <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N7" s="1">
+        <v>5</v>
+      </c>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
+      <c r="Q7" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8" s="7">
         <v>46032</v>
       </c>
@@ -731,8 +852,17 @@
         <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N8" s="1">
+        <v>6</v>
+      </c>
+      <c r="O8" s="6"/>
+      <c r="P8" s="6"/>
+      <c r="Q8" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9" s="7">
         <v>46033</v>
       </c>
@@ -750,8 +880,17 @@
         <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N9" s="1">
+        <v>7</v>
+      </c>
+      <c r="O9" s="6"/>
+      <c r="P9" s="6"/>
+      <c r="Q9" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10" s="7">
         <v>46034</v>
       </c>
@@ -769,8 +908,17 @@
         <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N10" s="1">
+        <v>8</v>
+      </c>
+      <c r="O10" s="6"/>
+      <c r="P10" s="6"/>
+      <c r="Q10" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11" s="7">
         <v>46035</v>
       </c>
@@ -788,8 +936,17 @@
         <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
         <v>4</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N11" s="1">
+        <v>9</v>
+      </c>
+      <c r="O11" s="6"/>
+      <c r="P11" s="6"/>
+      <c r="Q11" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12" s="7">
         <v>46036</v>
       </c>
@@ -807,23 +964,36 @@
         <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
         <v>2</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N12" s="1">
+        <v>10</v>
+      </c>
+      <c r="O12" s="6"/>
+      <c r="P12" s="6"/>
+      <c r="Q12" s="5">
+        <f>O12/60</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13" s="7">
         <v>46037</v>
       </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
+      <c r="B13" s="2">
+        <v>46037.561650115742</v>
+      </c>
+      <c r="C13" s="2">
+        <v>46037.750115740739</v>
+      </c>
       <c r="E13" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F13" s="5">
         <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14" s="7">
         <v>46038</v>
       </c>
@@ -838,7 +1008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15" s="7">
         <v>46039</v>
       </c>
@@ -853,7 +1023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16" s="7">
         <v>46040</v>
       </c>
@@ -1760,9 +1930,10 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-  <tableParts count="2">
+  <tableParts count="3">
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
   </tableParts>
 </worksheet>
 </file>
--- a/Baseline_docs/Time Sheet.xlsx
+++ b/Baseline_docs/Time Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wskinner\On Drive Files\Git\Secure-Multi-Layer-Network-Project---Capstone\Baseline_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEE8CFDE-EA3E-4B20-8276-93FE35141603}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{936FA93D-5D91-4E73-9991-C3DE0B274B96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -163,11 +163,11 @@
   </cellStyles>
   <dxfs count="21">
     <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -291,13 +291,13 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{0B533ACD-D878-47CD-A04A-12CDF739F4F4}" name="Table3" displayName="Table3" ref="N2:Q12" totalsRowShown="0" headerRowDxfId="4" dataDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{0B533ACD-D878-47CD-A04A-12CDF739F4F4}" name="Table3" displayName="Table3" ref="N2:Q12" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
   <autoFilter ref="N2:Q12" xr:uid="{0B533ACD-D878-47CD-A04A-12CDF739F4F4}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{CFA6B21D-D050-4C14-8F9A-5D7117BEA113}" name="Weeks" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{1CA91632-7336-422D-ABF9-C5E3F08EFBA5}" name="Minutes" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{BB9EBBBA-CBEE-4ACF-8769-1D581F89C8FE}" name="Hours" dataDxfId="0"/>
-    <tableColumn id="4" xr3:uid="{8911D862-F455-4BFD-BDFF-6839D678C8CE}" name="Hour %" dataDxfId="1">
+    <tableColumn id="3" xr3:uid="{BB9EBBBA-CBEE-4ACF-8769-1D581F89C8FE}" name="Hours" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{8911D862-F455-4BFD-BDFF-6839D678C8CE}" name="Hour %" dataDxfId="0">
       <calculatedColumnFormula>O3/60</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -666,15 +666,15 @@
       </c>
       <c r="H3" s="1">
         <f>SUM(E:E) + (I3*60) + SUM(D:D)</f>
-        <v>1579</v>
+        <v>1819</v>
       </c>
       <c r="I3" s="6">
         <f>SUM(F:F)</f>
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J3" s="5">
         <f>Table2[[#This Row],[Total Minutes]]/60</f>
-        <v>26.316666666666666</v>
+        <v>30.316666666666666</v>
       </c>
       <c r="K3" s="1" t="str">
         <f>IF(Table2[[#This Row],[Hour Percent]] &gt;= Table2[[#This Row],[Hours Needed]], "Hours have been met", "More hours needed")</f>
@@ -722,15 +722,15 @@
       </c>
       <c r="O4" s="6">
         <f>SUM(E10:E16) + (60*P4)</f>
-        <v>973</v>
+        <v>1213</v>
       </c>
       <c r="P4" s="6">
         <f>SUM(F10:F16)</f>
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="Q4" s="5">
         <f>O4/60</f>
-        <v>16.216666666666665</v>
+        <v>20.216666666666665</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.35">
@@ -766,7 +766,7 @@
         <v>0</v>
       </c>
       <c r="Q5" s="5">
-        <f t="shared" ref="Q5:Q12" si="0">O5/60</f>
+        <f t="shared" ref="Q5:Q11" si="0">O5/60</f>
         <v>0</v>
       </c>
     </row>
@@ -790,11 +790,11 @@
       </c>
       <c r="H6" s="3">
         <f ca="1">NOW()</f>
-        <v>46037.670982291667</v>
+        <v>46038.653016550925</v>
       </c>
       <c r="I6" s="4">
         <f ca="1">NOW()</f>
-        <v>46037.670982291667</v>
+        <v>46038.653016550925</v>
       </c>
       <c r="N6" s="1">
         <v>4</v>
@@ -997,15 +997,19 @@
       <c r="A14" s="7">
         <v>46038</v>
       </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
+      <c r="B14" s="2">
+        <v>46038.500196759262</v>
+      </c>
+      <c r="C14" s="2">
+        <v>46038.666898148149</v>
+      </c>
       <c r="E14" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
         <v>0</v>
       </c>
       <c r="F14" s="5">
         <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.35">

--- a/Baseline_docs/Time Sheet.xlsx
+++ b/Baseline_docs/Time Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wskinner\On Drive Files\Git\Secure-Multi-Layer-Network-Project---Capstone\Baseline_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{936FA93D-5D91-4E73-9991-C3DE0B274B96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5017F2EF-D7DF-43A7-A25E-015EAC089FA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="17">
   <si>
     <t>Day</t>
   </si>
@@ -666,15 +666,15 @@
       </c>
       <c r="H3" s="1">
         <f>SUM(E:E) + (I3*60) + SUM(D:D)</f>
-        <v>1819</v>
+        <v>2192</v>
       </c>
       <c r="I3" s="6">
         <f>SUM(F:F)</f>
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="J3" s="5">
         <f>Table2[[#This Row],[Total Minutes]]/60</f>
-        <v>30.316666666666666</v>
+        <v>36.533333333333331</v>
       </c>
       <c r="K3" s="1" t="str">
         <f>IF(Table2[[#This Row],[Hour Percent]] &gt;= Table2[[#This Row],[Hours Needed]], "Hours have been met", "More hours needed")</f>
@@ -759,15 +759,15 @@
       </c>
       <c r="O5" s="6">
         <f>SUM(E17:E23) + (60*P5)</f>
-        <v>0</v>
+        <v>373</v>
       </c>
       <c r="P5" s="6">
         <f>SUM(F17:F23)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q5" s="5">
         <f t="shared" ref="Q5:Q11" si="0">O5/60</f>
-        <v>0</v>
+        <v>6.2166666666666668</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.35">
@@ -790,11 +790,11 @@
       </c>
       <c r="H6" s="3">
         <f ca="1">NOW()</f>
-        <v>46038.653016550925</v>
+        <v>46041.759046874999</v>
       </c>
       <c r="I6" s="4">
         <f ca="1">NOW()</f>
-        <v>46038.653016550925</v>
+        <v>46041.759046874999</v>
       </c>
       <c r="N6" s="1">
         <v>4</v>
@@ -1016,8 +1016,12 @@
       <c r="A15" s="7">
         <v>46039</v>
       </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
+      <c r="B15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="E15" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
         <v>0</v>
@@ -1031,8 +1035,12 @@
       <c r="A16" s="7">
         <v>46040</v>
       </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
+      <c r="B16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="E16" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
         <v>0</v>
@@ -1046,15 +1054,19 @@
       <c r="A17" s="7">
         <v>46041</v>
       </c>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
+      <c r="B17" s="2">
+        <v>46041.499320138886</v>
+      </c>
+      <c r="C17" s="2">
+        <v>46041.758986921297</v>
+      </c>
       <c r="E17" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F17" s="5">
         <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">

--- a/Baseline_docs/Time Sheet.xlsx
+++ b/Baseline_docs/Time Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wskinner\On Drive Files\Git\Secure-Multi-Layer-Network-Project---Capstone\Baseline_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5017F2EF-D7DF-43A7-A25E-015EAC089FA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A046A932-7BAE-4921-83D6-AF5414FB47DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -666,19 +666,19 @@
       </c>
       <c r="H3" s="1">
         <f>SUM(E:E) + (I3*60) + SUM(D:D)</f>
-        <v>2192</v>
+        <v>2498</v>
       </c>
       <c r="I3" s="6">
         <f>SUM(F:F)</f>
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J3" s="5">
         <f>Table2[[#This Row],[Total Minutes]]/60</f>
-        <v>36.533333333333331</v>
+        <v>41.633333333333333</v>
       </c>
       <c r="K3" s="1" t="str">
         <f>IF(Table2[[#This Row],[Hour Percent]] &gt;= Table2[[#This Row],[Hours Needed]], "Hours have been met", "More hours needed")</f>
-        <v>More hours needed</v>
+        <v>Hours have been met</v>
       </c>
       <c r="L3" s="1">
         <v>40</v>
@@ -759,15 +759,15 @@
       </c>
       <c r="O5" s="6">
         <f>SUM(E17:E23) + (60*P5)</f>
-        <v>373</v>
+        <v>679</v>
       </c>
       <c r="P5" s="6">
         <f>SUM(F17:F23)</f>
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Q5" s="5">
         <f t="shared" ref="Q5:Q11" si="0">O5/60</f>
-        <v>6.2166666666666668</v>
+        <v>11.316666666666666</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.35">
@@ -790,11 +790,11 @@
       </c>
       <c r="H6" s="3">
         <f ca="1">NOW()</f>
-        <v>46041.759046874999</v>
+        <v>46042.707945138885</v>
       </c>
       <c r="I6" s="4">
         <f ca="1">NOW()</f>
-        <v>46041.759046874999</v>
+        <v>46042.707945138885</v>
       </c>
       <c r="N6" s="1">
         <v>4</v>
@@ -1073,15 +1073,19 @@
       <c r="A18" s="7">
         <v>46042</v>
       </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
+      <c r="B18" s="2">
+        <v>46042.495302777781</v>
+      </c>
+      <c r="C18" s="2">
+        <v>46042.708460648151</v>
+      </c>
       <c r="E18" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F18" s="5">
         <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">

--- a/Baseline_docs/Time Sheet.xlsx
+++ b/Baseline_docs/Time Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wskinner\On Drive Files\Git\Secure-Multi-Layer-Network-Project---Capstone\Baseline_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A046A932-7BAE-4921-83D6-AF5414FB47DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59073C80-37DC-4DBA-8E1C-3802BA7F0091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -790,17 +790,23 @@
       </c>
       <c r="H6" s="3">
         <f ca="1">NOW()</f>
-        <v>46042.707945138885</v>
+        <v>46043.496378703705</v>
       </c>
       <c r="I6" s="4">
         <f ca="1">NOW()</f>
-        <v>46042.707945138885</v>
+        <v>46043.496378703705</v>
       </c>
       <c r="N6" s="1">
         <v>4</v>
       </c>
-      <c r="O6" s="6"/>
-      <c r="P6" s="6"/>
+      <c r="O6" s="6">
+        <f>SUM(E24:E30) + (60*P6)</f>
+        <v>0</v>
+      </c>
+      <c r="P6" s="6">
+        <f>SUM(F24:F30)</f>
+        <v>0</v>
+      </c>
       <c r="Q6" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1092,7 +1098,9 @@
       <c r="A19" s="7">
         <v>46043</v>
       </c>
-      <c r="B19" s="2"/>
+      <c r="B19" s="2">
+        <v>46043.495493981478</v>
+      </c>
       <c r="C19" s="2"/>
       <c r="E19" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>

--- a/Baseline_docs/Time Sheet.xlsx
+++ b/Baseline_docs/Time Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wskinner\On Drive Files\Git\Secure-Multi-Layer-Network-Project---Capstone\Baseline_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59073C80-37DC-4DBA-8E1C-3802BA7F0091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D84FB547-DB25-4F33-810A-BE33C822F66B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -666,15 +666,15 @@
       </c>
       <c r="H3" s="1">
         <f>SUM(E:E) + (I3*60) + SUM(D:D)</f>
-        <v>2498</v>
+        <v>2925</v>
       </c>
       <c r="I3" s="6">
         <f>SUM(F:F)</f>
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="J3" s="5">
         <f>Table2[[#This Row],[Total Minutes]]/60</f>
-        <v>41.633333333333333</v>
+        <v>48.75</v>
       </c>
       <c r="K3" s="1" t="str">
         <f>IF(Table2[[#This Row],[Hour Percent]] &gt;= Table2[[#This Row],[Hours Needed]], "Hours have been met", "More hours needed")</f>
@@ -759,15 +759,15 @@
       </c>
       <c r="O5" s="6">
         <f>SUM(E17:E23) + (60*P5)</f>
-        <v>679</v>
+        <v>1106</v>
       </c>
       <c r="P5" s="6">
         <f>SUM(F17:F23)</f>
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="Q5" s="5">
         <f t="shared" ref="Q5:Q11" si="0">O5/60</f>
-        <v>11.316666666666666</v>
+        <v>18.433333333333334</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.35">
@@ -790,11 +790,11 @@
       </c>
       <c r="H6" s="3">
         <f ca="1">NOW()</f>
-        <v>46043.496378703705</v>
+        <v>46043.783585648147</v>
       </c>
       <c r="I6" s="4">
         <f ca="1">NOW()</f>
-        <v>46043.496378703705</v>
+        <v>46043.783585648147</v>
       </c>
       <c r="N6" s="1">
         <v>4</v>
@@ -1101,14 +1101,16 @@
       <c r="B19" s="2">
         <v>46043.495493981478</v>
       </c>
-      <c r="C19" s="2"/>
+      <c r="C19" s="2">
+        <v>46043.792025462964</v>
+      </c>
       <c r="E19" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F19" s="5">
         <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">

--- a/Baseline_docs/Time Sheet.xlsx
+++ b/Baseline_docs/Time Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wskinner\On Drive Files\Git\Secure-Multi-Layer-Network-Project---Capstone\Baseline_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D84FB547-DB25-4F33-810A-BE33C822F66B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F99AB878-21E0-45C0-97D9-A997C4D9ED6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="17">
   <si>
     <t>Day</t>
   </si>
@@ -666,22 +666,22 @@
       </c>
       <c r="H3" s="1">
         <f>SUM(E:E) + (I3*60) + SUM(D:D)</f>
-        <v>2925</v>
+        <v>3077</v>
       </c>
       <c r="I3" s="6">
         <f>SUM(F:F)</f>
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J3" s="5">
         <f>Table2[[#This Row],[Total Minutes]]/60</f>
-        <v>48.75</v>
+        <v>51.283333333333331</v>
       </c>
       <c r="K3" s="1" t="str">
         <f>IF(Table2[[#This Row],[Hour Percent]] &gt;= Table2[[#This Row],[Hours Needed]], "Hours have been met", "More hours needed")</f>
-        <v>Hours have been met</v>
+        <v>More hours needed</v>
       </c>
       <c r="L3" s="1">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="N3" s="1">
         <v>1</v>
@@ -759,15 +759,15 @@
       </c>
       <c r="O5" s="6">
         <f>SUM(E17:E23) + (60*P5)</f>
-        <v>1106</v>
+        <v>1258</v>
       </c>
       <c r="P5" s="6">
         <f>SUM(F17:F23)</f>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Q5" s="5">
         <f t="shared" ref="Q5:Q11" si="0">O5/60</f>
-        <v>18.433333333333334</v>
+        <v>20.966666666666665</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.35">
@@ -790,11 +790,11 @@
       </c>
       <c r="H6" s="3">
         <f ca="1">NOW()</f>
-        <v>46043.783585648147</v>
+        <v>46044.699333796299</v>
       </c>
       <c r="I6" s="4">
         <f ca="1">NOW()</f>
-        <v>46043.783585648147</v>
+        <v>46044.699333796299</v>
       </c>
       <c r="N6" s="1">
         <v>4</v>
@@ -1117,15 +1117,19 @@
       <c r="A20" s="7">
         <v>46044</v>
       </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
+      <c r="B20" s="2">
+        <v>46044.593530092592</v>
+      </c>
+      <c r="C20" s="2">
+        <v>46044.699271759258</v>
+      </c>
       <c r="E20" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F20" s="5">
         <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
@@ -1147,8 +1151,12 @@
       <c r="A22" s="7">
         <v>46046</v>
       </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
+      <c r="B22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="E22" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
         <v>0</v>
@@ -1162,8 +1170,12 @@
       <c r="A23" s="7">
         <v>46047</v>
       </c>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
+      <c r="B23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="E23" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
         <v>0</v>

--- a/Baseline_docs/Time Sheet.xlsx
+++ b/Baseline_docs/Time Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wskinner\On Drive Files\Git\Secure-Multi-Layer-Network-Project---Capstone\Baseline_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F99AB878-21E0-45C0-97D9-A997C4D9ED6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E60F1CC-1625-4F71-B9EC-C754194061BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -665,19 +665,19 @@
         <v>1</v>
       </c>
       <c r="H3" s="1">
-        <f>SUM(E:E) + (I3*60) + SUM(D:D)</f>
-        <v>3077</v>
+        <f ca="1">SUM(E:E) + (I3*60) + SUM(D:D)</f>
+        <v>3222</v>
       </c>
       <c r="I3" s="6">
-        <f>SUM(F:F)</f>
-        <v>47</v>
+        <f ca="1">SUM(F:F)</f>
+        <v>49</v>
       </c>
       <c r="J3" s="5">
-        <f>Table2[[#This Row],[Total Minutes]]/60</f>
-        <v>51.283333333333331</v>
+        <f ca="1">Table2[[#This Row],[Total Minutes]]/60</f>
+        <v>53.7</v>
       </c>
       <c r="K3" s="1" t="str">
-        <f>IF(Table2[[#This Row],[Hour Percent]] &gt;= Table2[[#This Row],[Hours Needed]], "Hours have been met", "More hours needed")</f>
+        <f ca="1">IF(Table2[[#This Row],[Hour Percent]] &gt;= Table2[[#This Row],[Hours Needed]], "Hours have been met", "More hours needed")</f>
         <v>More hours needed</v>
       </c>
       <c r="L3" s="1">
@@ -758,16 +758,16 @@
         <v>3</v>
       </c>
       <c r="O5" s="6">
-        <f>SUM(E17:E23) + (60*P5)</f>
-        <v>1258</v>
+        <f ca="1">SUM(E17:E23) + (60*P5)</f>
+        <v>1403</v>
       </c>
       <c r="P5" s="6">
-        <f>SUM(F17:F23)</f>
-        <v>20</v>
+        <f ca="1">SUM(F17:F23)</f>
+        <v>22</v>
       </c>
       <c r="Q5" s="5">
-        <f t="shared" ref="Q5:Q11" si="0">O5/60</f>
-        <v>20.966666666666665</v>
+        <f t="shared" ref="Q5:Q11" ca="1" si="0">O5/60</f>
+        <v>23.383333333333333</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.35">
@@ -790,11 +790,11 @@
       </c>
       <c r="H6" s="3">
         <f ca="1">NOW()</f>
-        <v>46044.699333796299</v>
+        <v>46045.667283564813</v>
       </c>
       <c r="I6" s="4">
         <f ca="1">NOW()</f>
-        <v>46044.699333796299</v>
+        <v>46045.667283564813</v>
       </c>
       <c r="N6" s="1">
         <v>4</v>
@@ -1136,15 +1136,20 @@
       <c r="A21" s="7">
         <v>46045</v>
       </c>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
+      <c r="B21" s="2">
+        <v>46045.56648645833</v>
+      </c>
+      <c r="C21" s="4">
+        <f ca="1">NOW()</f>
+        <v>46045.667283564813</v>
+      </c>
       <c r="E21" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
+        <f ca="1">IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>25</v>
       </c>
       <c r="F21" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
+        <f ca="1">IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">

--- a/Baseline_docs/Time Sheet.xlsx
+++ b/Baseline_docs/Time Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wskinner\On Drive Files\Git\Secure-Multi-Layer-Network-Project---Capstone\Baseline_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E60F1CC-1625-4F71-B9EC-C754194061BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD655043-805A-4B45-924F-83EF6F797F4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -665,19 +665,19 @@
         <v>1</v>
       </c>
       <c r="H3" s="1">
-        <f ca="1">SUM(E:E) + (I3*60) + SUM(D:D)</f>
-        <v>3222</v>
+        <f>SUM(E:E) + (I3*60) + SUM(D:D)</f>
+        <v>3792</v>
       </c>
       <c r="I3" s="6">
-        <f ca="1">SUM(F:F)</f>
-        <v>49</v>
+        <f>SUM(F:F)</f>
+        <v>58</v>
       </c>
       <c r="J3" s="5">
-        <f ca="1">Table2[[#This Row],[Total Minutes]]/60</f>
-        <v>53.7</v>
+        <f>Table2[[#This Row],[Total Minutes]]/60</f>
+        <v>63.2</v>
       </c>
       <c r="K3" s="1" t="str">
-        <f ca="1">IF(Table2[[#This Row],[Hour Percent]] &gt;= Table2[[#This Row],[Hours Needed]], "Hours have been met", "More hours needed")</f>
+        <f>IF(Table2[[#This Row],[Hour Percent]] &gt;= Table2[[#This Row],[Hours Needed]], "Hours have been met", "More hours needed")</f>
         <v>More hours needed</v>
       </c>
       <c r="L3" s="1">
@@ -758,16 +758,16 @@
         <v>3</v>
       </c>
       <c r="O5" s="6">
-        <f ca="1">SUM(E17:E23) + (60*P5)</f>
-        <v>1403</v>
+        <f>SUM(E17:E23) + (60*P5)</f>
+        <v>1382</v>
       </c>
       <c r="P5" s="6">
-        <f ca="1">SUM(F17:F23)</f>
+        <f>SUM(F17:F23)</f>
         <v>22</v>
       </c>
       <c r="Q5" s="5">
-        <f t="shared" ref="Q5:Q11" ca="1" si="0">O5/60</f>
-        <v>23.383333333333333</v>
+        <f t="shared" ref="Q5:Q11" si="0">O5/60</f>
+        <v>23.033333333333335</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.35">
@@ -790,26 +790,26 @@
       </c>
       <c r="H6" s="3">
         <f ca="1">NOW()</f>
-        <v>46045.667283564813</v>
+        <v>46048.931233912037</v>
       </c>
       <c r="I6" s="4">
         <f ca="1">NOW()</f>
-        <v>46045.667283564813</v>
+        <v>46048.931233912037</v>
       </c>
       <c r="N6" s="1">
         <v>4</v>
       </c>
       <c r="O6" s="6">
         <f>SUM(E24:E30) + (60*P6)</f>
-        <v>0</v>
+        <v>591</v>
       </c>
       <c r="P6" s="6">
         <f>SUM(F24:F30)</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q6" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>9.85</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.35">
@@ -1139,16 +1139,15 @@
       <c r="B21" s="2">
         <v>46045.56648645833</v>
       </c>
-      <c r="C21" s="4">
-        <f ca="1">NOW()</f>
-        <v>46045.667283564813</v>
+      <c r="C21" s="2">
+        <v>46045.653171296297</v>
       </c>
       <c r="E21" s="5">
-        <f ca="1">IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>25</v>
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>4</v>
       </c>
       <c r="F21" s="5">
-        <f ca="1">IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
         <v>2</v>
       </c>
     </row>
@@ -1194,15 +1193,19 @@
       <c r="A24" s="7">
         <v>46048</v>
       </c>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
+      <c r="B24" s="2">
+        <v>46048.520721759262</v>
+      </c>
+      <c r="C24" s="2">
+        <v>46048.931156134262</v>
+      </c>
       <c r="E24" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="F24" s="5">
         <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">

--- a/Baseline_docs/Time Sheet.xlsx
+++ b/Baseline_docs/Time Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wskinner\On Drive Files\Git\Secure-Multi-Layer-Network-Project---Capstone\Baseline_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD655043-805A-4B45-924F-83EF6F797F4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA1739B6-63FB-4EB9-96CD-65F0B782F2C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -666,15 +666,15 @@
       </c>
       <c r="H3" s="1">
         <f>SUM(E:E) + (I3*60) + SUM(D:D)</f>
-        <v>3792</v>
+        <v>4109</v>
       </c>
       <c r="I3" s="6">
         <f>SUM(F:F)</f>
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="J3" s="5">
         <f>Table2[[#This Row],[Total Minutes]]/60</f>
-        <v>63.2</v>
+        <v>68.483333333333334</v>
       </c>
       <c r="K3" s="1" t="str">
         <f>IF(Table2[[#This Row],[Hour Percent]] &gt;= Table2[[#This Row],[Hours Needed]], "Hours have been met", "More hours needed")</f>
@@ -790,26 +790,26 @@
       </c>
       <c r="H6" s="3">
         <f ca="1">NOW()</f>
-        <v>46048.931233912037</v>
+        <v>46049.74670520833</v>
       </c>
       <c r="I6" s="4">
         <f ca="1">NOW()</f>
-        <v>46048.931233912037</v>
+        <v>46049.74670520833</v>
       </c>
       <c r="N6" s="1">
         <v>4</v>
       </c>
       <c r="O6" s="6">
         <f>SUM(E24:E30) + (60*P6)</f>
-        <v>591</v>
+        <v>908</v>
       </c>
       <c r="P6" s="6">
         <f>SUM(F24:F30)</f>
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="Q6" s="5">
         <f t="shared" si="0"/>
-        <v>9.85</v>
+        <v>15.133333333333333</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.35">
@@ -1197,30 +1197,34 @@
         <v>46048.520721759262</v>
       </c>
       <c r="C24" s="2">
-        <v>46048.931156134262</v>
+        <v>46048.985324074078</v>
       </c>
       <c r="E24" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>51</v>
+        <v>9</v>
       </c>
       <c r="F24" s="5">
         <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="7">
         <v>46049</v>
       </c>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
+      <c r="B25" s="2">
+        <v>46049.583865740744</v>
+      </c>
+      <c r="C25" s="2">
+        <v>46049.750069444446</v>
+      </c>
       <c r="E25" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="F25" s="5">
         <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">

--- a/Baseline_docs/Time Sheet.xlsx
+++ b/Baseline_docs/Time Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wskinner\On Drive Files\Git\Secure-Multi-Layer-Network-Project---Capstone\Baseline_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA1739B6-63FB-4EB9-96CD-65F0B782F2C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4675A381-77A7-41CB-BB9D-C10F5C810F36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -666,15 +666,15 @@
       </c>
       <c r="H3" s="1">
         <f>SUM(E:E) + (I3*60) + SUM(D:D)</f>
-        <v>4109</v>
+        <v>4344</v>
       </c>
       <c r="I3" s="6">
         <f>SUM(F:F)</f>
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J3" s="5">
         <f>Table2[[#This Row],[Total Minutes]]/60</f>
-        <v>68.483333333333334</v>
+        <v>72.400000000000006</v>
       </c>
       <c r="K3" s="1" t="str">
         <f>IF(Table2[[#This Row],[Hour Percent]] &gt;= Table2[[#This Row],[Hours Needed]], "Hours have been met", "More hours needed")</f>
@@ -790,26 +790,26 @@
       </c>
       <c r="H6" s="3">
         <f ca="1">NOW()</f>
-        <v>46049.74670520833</v>
+        <v>46050.658785300926</v>
       </c>
       <c r="I6" s="4">
         <f ca="1">NOW()</f>
-        <v>46049.74670520833</v>
+        <v>46050.658785300926</v>
       </c>
       <c r="N6" s="1">
         <v>4</v>
       </c>
       <c r="O6" s="6">
         <f>SUM(E24:E30) + (60*P6)</f>
-        <v>908</v>
+        <v>1143</v>
       </c>
       <c r="P6" s="6">
         <f>SUM(F24:F30)</f>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q6" s="5">
         <f t="shared" si="0"/>
-        <v>15.133333333333333</v>
+        <v>19.05</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.35">
@@ -833,8 +833,14 @@
       <c r="N7" s="1">
         <v>5</v>
       </c>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
+      <c r="O7" s="6">
+        <f>SUM(E31:E37) + (60*P7)</f>
+        <v>0</v>
+      </c>
+      <c r="P7" s="6">
+        <f>SUM(F31:F37)</f>
+        <v>0</v>
+      </c>
       <c r="Q7" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1231,15 +1237,19 @@
       <c r="A26" s="7">
         <v>46050</v>
       </c>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
+      <c r="B26" s="2">
+        <v>46050.504202662036</v>
+      </c>
+      <c r="C26" s="2">
+        <v>46050.667615740742</v>
+      </c>
       <c r="E26" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="F26" s="5">
         <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">

--- a/Baseline_docs/Time Sheet.xlsx
+++ b/Baseline_docs/Time Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wskinner\On Drive Files\Git\Secure-Multi-Layer-Network-Project---Capstone\Baseline_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4675A381-77A7-41CB-BB9D-C10F5C810F36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{728507D7-BF99-450A-9D07-9C42F7B2786A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -790,11 +790,11 @@
       </c>
       <c r="H6" s="3">
         <f ca="1">NOW()</f>
-        <v>46050.658785300926</v>
+        <v>46051.575703587965</v>
       </c>
       <c r="I6" s="4">
         <f ca="1">NOW()</f>
-        <v>46050.658785300926</v>
+        <v>46051.575703587965</v>
       </c>
       <c r="N6" s="1">
         <v>4</v>
@@ -1256,7 +1256,9 @@
       <c r="A27" s="7">
         <v>46051</v>
       </c>
-      <c r="B27" s="2"/>
+      <c r="B27" s="2">
+        <v>46051.575492939817</v>
+      </c>
       <c r="C27" s="2"/>
       <c r="E27" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>

--- a/Baseline_docs/Time Sheet.xlsx
+++ b/Baseline_docs/Time Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wskinner\On Drive Files\Git\Secure-Multi-Layer-Network-Project---Capstone\Baseline_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{728507D7-BF99-450A-9D07-9C42F7B2786A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4E1B985-D965-4FEF-A6A3-8E0F4F0E1A60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -666,15 +666,15 @@
       </c>
       <c r="H3" s="1">
         <f>SUM(E:E) + (I3*60) + SUM(D:D)</f>
-        <v>4344</v>
+        <v>4546</v>
       </c>
       <c r="I3" s="6">
         <f>SUM(F:F)</f>
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="J3" s="5">
         <f>Table2[[#This Row],[Total Minutes]]/60</f>
-        <v>72.400000000000006</v>
+        <v>75.766666666666666</v>
       </c>
       <c r="K3" s="1" t="str">
         <f>IF(Table2[[#This Row],[Hour Percent]] &gt;= Table2[[#This Row],[Hours Needed]], "Hours have been met", "More hours needed")</f>
@@ -790,26 +790,26 @@
       </c>
       <c r="H6" s="3">
         <f ca="1">NOW()</f>
-        <v>46051.575703587965</v>
+        <v>46051.708415393521</v>
       </c>
       <c r="I6" s="4">
         <f ca="1">NOW()</f>
-        <v>46051.575703587965</v>
+        <v>46051.708415393521</v>
       </c>
       <c r="N6" s="1">
         <v>4</v>
       </c>
       <c r="O6" s="6">
         <f>SUM(E24:E30) + (60*P6)</f>
-        <v>1143</v>
+        <v>1345</v>
       </c>
       <c r="P6" s="6">
         <f>SUM(F24:F30)</f>
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="Q6" s="5">
         <f t="shared" si="0"/>
-        <v>19.05</v>
+        <v>22.416666666666668</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.35">
@@ -1259,14 +1259,16 @@
       <c r="B27" s="2">
         <v>46051.575492939817</v>
       </c>
-      <c r="C27" s="2"/>
+      <c r="C27" s="2">
+        <v>46051.715775462966</v>
+      </c>
       <c r="E27" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F27" s="5">
         <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">

--- a/Baseline_docs/Time Sheet.xlsx
+++ b/Baseline_docs/Time Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wskinner\On Drive Files\Git\Secure-Multi-Layer-Network-Project---Capstone\Baseline_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4E1B985-D965-4FEF-A6A3-8E0F4F0E1A60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E3252AD-8B74-49A3-81C7-67622584DAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -666,15 +666,15 @@
       </c>
       <c r="H3" s="1">
         <f>SUM(E:E) + (I3*60) + SUM(D:D)</f>
-        <v>4546</v>
+        <v>4622</v>
       </c>
       <c r="I3" s="6">
         <f>SUM(F:F)</f>
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J3" s="5">
         <f>Table2[[#This Row],[Total Minutes]]/60</f>
-        <v>75.766666666666666</v>
+        <v>77.033333333333331</v>
       </c>
       <c r="K3" s="1" t="str">
         <f>IF(Table2[[#This Row],[Hour Percent]] &gt;= Table2[[#This Row],[Hours Needed]], "Hours have been met", "More hours needed")</f>
@@ -790,26 +790,26 @@
       </c>
       <c r="H6" s="3">
         <f ca="1">NOW()</f>
-        <v>46051.708415393521</v>
+        <v>46052.565440740742</v>
       </c>
       <c r="I6" s="4">
         <f ca="1">NOW()</f>
-        <v>46051.708415393521</v>
+        <v>46052.565440740742</v>
       </c>
       <c r="N6" s="1">
         <v>4</v>
       </c>
       <c r="O6" s="6">
         <f>SUM(E24:E30) + (60*P6)</f>
-        <v>1345</v>
+        <v>1421</v>
       </c>
       <c r="P6" s="6">
         <f>SUM(F24:F30)</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q6" s="5">
         <f t="shared" si="0"/>
-        <v>22.416666666666668</v>
+        <v>23.683333333333334</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.35">
@@ -1275,15 +1275,19 @@
       <c r="A28" s="7">
         <v>46052</v>
       </c>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
+      <c r="B28" s="2">
+        <v>46052.52367696759</v>
+      </c>
+      <c r="C28" s="2">
+        <v>46052.57707175926</v>
+      </c>
       <c r="E28" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F28" s="5">
         <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">

--- a/Baseline_docs/Time Sheet.xlsx
+++ b/Baseline_docs/Time Sheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wskinner\On Drive Files\Git\Secure-Multi-Layer-Network-Project---Capstone\Baseline_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E3252AD-8B74-49A3-81C7-67622584DAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24A0C7C7-29C4-493D-854B-5C6B6136F269}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="17">
   <si>
     <t>Day</t>
   </si>
@@ -666,7 +666,7 @@
       </c>
       <c r="H3" s="1">
         <f>SUM(E:E) + (I3*60) + SUM(D:D)</f>
-        <v>4622</v>
+        <v>4632</v>
       </c>
       <c r="I3" s="6">
         <f>SUM(F:F)</f>
@@ -674,21 +674,21 @@
       </c>
       <c r="J3" s="5">
         <f>Table2[[#This Row],[Total Minutes]]/60</f>
-        <v>77.033333333333331</v>
+        <v>77.2</v>
       </c>
       <c r="K3" s="1" t="str">
         <f>IF(Table2[[#This Row],[Hour Percent]] &gt;= Table2[[#This Row],[Hours Needed]], "Hours have been met", "More hours needed")</f>
         <v>More hours needed</v>
       </c>
       <c r="L3" s="1">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="N3" s="1">
         <v>1</v>
       </c>
       <c r="O3" s="6">
-        <f>SUM(E3:E9) + (60*P3)</f>
-        <v>601</v>
+        <f>SUM(D3:E9) + (60*P3)</f>
+        <v>606</v>
       </c>
       <c r="P3" s="6">
         <f>SUM(F3:F9)</f>
@@ -696,7 +696,7 @@
       </c>
       <c r="Q3" s="5">
         <f>O3/60</f>
-        <v>10.016666666666667</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.35">
@@ -721,7 +721,7 @@
         <v>2</v>
       </c>
       <c r="O4" s="6">
-        <f>SUM(E10:E16) + (60*P4)</f>
+        <f>SUM(D10:E16) + (60*P4)</f>
         <v>1213</v>
       </c>
       <c r="P4" s="6">
@@ -758,7 +758,7 @@
         <v>3</v>
       </c>
       <c r="O5" s="6">
-        <f>SUM(E17:E23) + (60*P5)</f>
+        <f>SUM(D17:E23) + (60*P5)</f>
         <v>1382</v>
       </c>
       <c r="P5" s="6">
@@ -790,17 +790,17 @@
       </c>
       <c r="H6" s="3">
         <f ca="1">NOW()</f>
-        <v>46052.565440740742</v>
+        <v>46055.511901736114</v>
       </c>
       <c r="I6" s="4">
         <f ca="1">NOW()</f>
-        <v>46052.565440740742</v>
+        <v>46055.511901736114</v>
       </c>
       <c r="N6" s="1">
         <v>4</v>
       </c>
       <c r="O6" s="6">
-        <f>SUM(E24:E30) + (60*P6)</f>
+        <f>SUM(D24:E30) + (60*P6)</f>
         <v>1421</v>
       </c>
       <c r="P6" s="6">
@@ -834,8 +834,8 @@
         <v>5</v>
       </c>
       <c r="O7" s="6">
-        <f>SUM(E31:E37) + (60*P7)</f>
-        <v>0</v>
+        <f>SUM(D31:E37) + (60*P7)</f>
+        <v>10</v>
       </c>
       <c r="P7" s="6">
         <f>SUM(F31:F37)</f>
@@ -843,7 +843,7 @@
       </c>
       <c r="Q7" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.16666666666666666</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.35">
@@ -867,8 +867,14 @@
       <c r="N8" s="1">
         <v>6</v>
       </c>
-      <c r="O8" s="6"/>
-      <c r="P8" s="6"/>
+      <c r="O8" s="6">
+        <f>SUM(D38:E44) + (60*P8)</f>
+        <v>0</v>
+      </c>
+      <c r="P8" s="6">
+        <f>SUM(F38:F44)</f>
+        <v>0</v>
+      </c>
       <c r="Q8" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1294,8 +1300,12 @@
       <c r="A29" s="7">
         <v>46053</v>
       </c>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
+      <c r="B29" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="E29" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
         <v>0</v>
@@ -1309,8 +1319,12 @@
       <c r="A30" s="7">
         <v>46054</v>
       </c>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
+      <c r="B30" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="E30" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
         <v>0</v>
@@ -1324,8 +1338,13 @@
       <c r="A31" s="7">
         <v>46055</v>
       </c>
-      <c r="B31" s="2"/>
+      <c r="B31" s="2">
+        <v>46055.511829745374</v>
+      </c>
       <c r="C31" s="2"/>
+      <c r="D31" s="5">
+        <v>10</v>
+      </c>
       <c r="E31" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
         <v>0</v>

--- a/Baseline_docs/Time Sheet.xlsx
+++ b/Baseline_docs/Time Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wskinner\On Drive Files\Git\Secure-Multi-Layer-Network-Project---Capstone\Baseline_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24A0C7C7-29C4-493D-854B-5C6B6136F269}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8ECD0C0-B6E5-4AE2-A280-78C99AA001BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -666,15 +666,15 @@
       </c>
       <c r="H3" s="1">
         <f>SUM(E:E) + (I3*60) + SUM(D:D)</f>
-        <v>4632</v>
+        <v>4765</v>
       </c>
       <c r="I3" s="6">
         <f>SUM(F:F)</f>
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J3" s="5">
         <f>Table2[[#This Row],[Total Minutes]]/60</f>
-        <v>77.2</v>
+        <v>79.416666666666671</v>
       </c>
       <c r="K3" s="1" t="str">
         <f>IF(Table2[[#This Row],[Hour Percent]] &gt;= Table2[[#This Row],[Hours Needed]], "Hours have been met", "More hours needed")</f>
@@ -790,11 +790,11 @@
       </c>
       <c r="H6" s="3">
         <f ca="1">NOW()</f>
-        <v>46055.511901736114</v>
+        <v>46055.581111574073</v>
       </c>
       <c r="I6" s="4">
         <f ca="1">NOW()</f>
-        <v>46055.511901736114</v>
+        <v>46055.581111574073</v>
       </c>
       <c r="N6" s="1">
         <v>4</v>
@@ -835,15 +835,15 @@
       </c>
       <c r="O7" s="6">
         <f>SUM(D31:E37) + (60*P7)</f>
-        <v>10</v>
+        <v>143</v>
       </c>
       <c r="P7" s="6">
         <f>SUM(F31:F37)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q7" s="5">
         <f t="shared" si="0"/>
-        <v>0.16666666666666666</v>
+        <v>2.3833333333333333</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.35">
@@ -1341,17 +1341,19 @@
       <c r="B31" s="2">
         <v>46055.511829745374</v>
       </c>
-      <c r="C31" s="2"/>
+      <c r="C31" s="2">
+        <v>46055.604791666665</v>
+      </c>
       <c r="D31" s="5">
         <v>10</v>
       </c>
       <c r="E31" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F31" s="5">
         <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">

--- a/Baseline_docs/Time Sheet.xlsx
+++ b/Baseline_docs/Time Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wskinner\On Drive Files\Git\Secure-Multi-Layer-Network-Project---Capstone\Baseline_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8ECD0C0-B6E5-4AE2-A280-78C99AA001BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B194186-70C2-4EA8-9116-23EE11EA24A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -666,15 +666,15 @@
       </c>
       <c r="H3" s="1">
         <f>SUM(E:E) + (I3*60) + SUM(D:D)</f>
-        <v>4765</v>
+        <v>5009</v>
       </c>
       <c r="I3" s="6">
         <f>SUM(F:F)</f>
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="J3" s="5">
         <f>Table2[[#This Row],[Total Minutes]]/60</f>
-        <v>79.416666666666671</v>
+        <v>83.483333333333334</v>
       </c>
       <c r="K3" s="1" t="str">
         <f>IF(Table2[[#This Row],[Hour Percent]] &gt;= Table2[[#This Row],[Hours Needed]], "Hours have been met", "More hours needed")</f>
@@ -790,11 +790,11 @@
       </c>
       <c r="H6" s="3">
         <f ca="1">NOW()</f>
-        <v>46055.581111574073</v>
+        <v>46056.638255555554</v>
       </c>
       <c r="I6" s="4">
         <f ca="1">NOW()</f>
-        <v>46055.581111574073</v>
+        <v>46056.638255555554</v>
       </c>
       <c r="N6" s="1">
         <v>4</v>
@@ -835,15 +835,15 @@
       </c>
       <c r="O7" s="6">
         <f>SUM(D31:E37) + (60*P7)</f>
-        <v>143</v>
+        <v>387</v>
       </c>
       <c r="P7" s="6">
         <f>SUM(F31:F37)</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q7" s="5">
         <f t="shared" si="0"/>
-        <v>2.3833333333333333</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.35">
@@ -1360,15 +1360,19 @@
       <c r="A32" s="7">
         <v>46056</v>
       </c>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
+      <c r="B32" s="2">
+        <v>46056.580678124999</v>
+      </c>
+      <c r="C32" s="2">
+        <v>46056.75068287037</v>
+      </c>
       <c r="E32" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F32" s="5">
         <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">

--- a/Baseline_docs/Time Sheet.xlsx
+++ b/Baseline_docs/Time Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wskinner\On Drive Files\Git\Secure-Multi-Layer-Network-Project---Capstone\Baseline_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B194186-70C2-4EA8-9116-23EE11EA24A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E311EBB1-BAEB-4126-9BB9-F8B95B770BDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -790,11 +790,11 @@
       </c>
       <c r="H6" s="3">
         <f ca="1">NOW()</f>
-        <v>46056.638255555554</v>
+        <v>46057.537573726855</v>
       </c>
       <c r="I6" s="4">
         <f ca="1">NOW()</f>
-        <v>46056.638255555554</v>
+        <v>46057.537573726855</v>
       </c>
       <c r="N6" s="1">
         <v>4</v>
@@ -1379,7 +1379,9 @@
       <c r="A33" s="7">
         <v>46057</v>
       </c>
-      <c r="B33" s="2"/>
+      <c r="B33" s="2">
+        <v>46057.535749884257</v>
+      </c>
       <c r="C33" s="2"/>
       <c r="E33" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>

--- a/Baseline_docs/Time Sheet.xlsx
+++ b/Baseline_docs/Time Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wskinner\On Drive Files\Git\Secure-Multi-Layer-Network-Project---Capstone\Baseline_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E311EBB1-BAEB-4126-9BB9-F8B95B770BDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCA50D43-59B1-49A3-B228-FB42A7C742F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -666,15 +666,15 @@
       </c>
       <c r="H3" s="1">
         <f>SUM(E:E) + (I3*60) + SUM(D:D)</f>
-        <v>5009</v>
+        <v>5229</v>
       </c>
       <c r="I3" s="6">
         <f>SUM(F:F)</f>
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="J3" s="5">
         <f>Table2[[#This Row],[Total Minutes]]/60</f>
-        <v>83.483333333333334</v>
+        <v>87.15</v>
       </c>
       <c r="K3" s="1" t="str">
         <f>IF(Table2[[#This Row],[Hour Percent]] &gt;= Table2[[#This Row],[Hours Needed]], "Hours have been met", "More hours needed")</f>
@@ -790,11 +790,11 @@
       </c>
       <c r="H6" s="3">
         <f ca="1">NOW()</f>
-        <v>46057.537573726855</v>
+        <v>46057.688575810185</v>
       </c>
       <c r="I6" s="4">
         <f ca="1">NOW()</f>
-        <v>46057.537573726855</v>
+        <v>46057.688575810185</v>
       </c>
       <c r="N6" s="1">
         <v>4</v>
@@ -835,15 +835,15 @@
       </c>
       <c r="O7" s="6">
         <f>SUM(D31:E37) + (60*P7)</f>
-        <v>387</v>
+        <v>607</v>
       </c>
       <c r="P7" s="6">
         <f>SUM(F31:F37)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Q7" s="5">
         <f t="shared" si="0"/>
-        <v>6.45</v>
+        <v>10.116666666666667</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.35">
@@ -1382,14 +1382,16 @@
       <c r="B33" s="2">
         <v>46057.535749884257</v>
       </c>
-      <c r="C33" s="2"/>
+      <c r="C33" s="2">
+        <v>46057.688575</v>
+      </c>
       <c r="E33" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F33" s="5">
         <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">

--- a/Baseline_docs/Time Sheet.xlsx
+++ b/Baseline_docs/Time Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wskinner\On Drive Files\Git\Secure-Multi-Layer-Network-Project---Capstone\Baseline_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCA50D43-59B1-49A3-B228-FB42A7C742F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B4AE7F6-5722-4D5F-AE40-2A43A30404C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -666,15 +666,15 @@
       </c>
       <c r="H3" s="1">
         <f>SUM(E:E) + (I3*60) + SUM(D:D)</f>
-        <v>5229</v>
+        <v>5789</v>
       </c>
       <c r="I3" s="6">
         <f>SUM(F:F)</f>
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="J3" s="5">
         <f>Table2[[#This Row],[Total Minutes]]/60</f>
-        <v>87.15</v>
+        <v>96.483333333333334</v>
       </c>
       <c r="K3" s="1" t="str">
         <f>IF(Table2[[#This Row],[Hour Percent]] &gt;= Table2[[#This Row],[Hours Needed]], "Hours have been met", "More hours needed")</f>
@@ -790,11 +790,11 @@
       </c>
       <c r="H6" s="3">
         <f ca="1">NOW()</f>
-        <v>46057.688575810185</v>
+        <v>46059.513007407404</v>
       </c>
       <c r="I6" s="4">
         <f ca="1">NOW()</f>
-        <v>46057.688575810185</v>
+        <v>46059.513007407404</v>
       </c>
       <c r="N6" s="1">
         <v>4</v>
@@ -835,15 +835,15 @@
       </c>
       <c r="O7" s="6">
         <f>SUM(D31:E37) + (60*P7)</f>
-        <v>607</v>
+        <v>1167</v>
       </c>
       <c r="P7" s="6">
         <f>SUM(F31:F37)</f>
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="Q7" s="5">
         <f t="shared" si="0"/>
-        <v>10.116666666666667</v>
+        <v>19.45</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.35">
@@ -1398,22 +1398,28 @@
       <c r="A34" s="7">
         <v>46058</v>
       </c>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
+      <c r="B34" s="2">
+        <v>46058.569537037038</v>
+      </c>
+      <c r="C34" s="2">
+        <v>46058.958425925928</v>
+      </c>
       <c r="E34" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F34" s="5">
         <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="7">
         <v>46059</v>
       </c>
-      <c r="B35" s="2"/>
+      <c r="B35" s="2">
+        <v>46059.513006597219</v>
+      </c>
       <c r="C35" s="2"/>
       <c r="E35" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>

--- a/Baseline_docs/Time Sheet.xlsx
+++ b/Baseline_docs/Time Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wskinner\On Drive Files\Git\Secure-Multi-Layer-Network-Project---Capstone\Baseline_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B4AE7F6-5722-4D5F-AE40-2A43A30404C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C5830CB-1428-41CC-BA61-283820DCB033}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -666,15 +666,15 @@
       </c>
       <c r="H3" s="1">
         <f>SUM(E:E) + (I3*60) + SUM(D:D)</f>
-        <v>5789</v>
+        <v>5935</v>
       </c>
       <c r="I3" s="6">
         <f>SUM(F:F)</f>
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="J3" s="5">
         <f>Table2[[#This Row],[Total Minutes]]/60</f>
-        <v>96.483333333333334</v>
+        <v>98.916666666666671</v>
       </c>
       <c r="K3" s="1" t="str">
         <f>IF(Table2[[#This Row],[Hour Percent]] &gt;= Table2[[#This Row],[Hours Needed]], "Hours have been met", "More hours needed")</f>
@@ -790,11 +790,11 @@
       </c>
       <c r="H6" s="3">
         <f ca="1">NOW()</f>
-        <v>46059.513007407404</v>
+        <v>46059.614429398149</v>
       </c>
       <c r="I6" s="4">
         <f ca="1">NOW()</f>
-        <v>46059.513007407404</v>
+        <v>46059.614429398149</v>
       </c>
       <c r="N6" s="1">
         <v>4</v>
@@ -835,15 +835,15 @@
       </c>
       <c r="O7" s="6">
         <f>SUM(D31:E37) + (60*P7)</f>
-        <v>1167</v>
+        <v>1313</v>
       </c>
       <c r="P7" s="6">
         <f>SUM(F31:F37)</f>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Q7" s="5">
         <f t="shared" si="0"/>
-        <v>19.45</v>
+        <v>21.883333333333333</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.35">
@@ -1420,14 +1420,16 @@
       <c r="B35" s="2">
         <v>46059.513006597219</v>
       </c>
-      <c r="C35" s="2"/>
+      <c r="C35" s="2">
+        <v>46059.61440972222</v>
+      </c>
       <c r="E35" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F35" s="5">
         <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">

--- a/Baseline_docs/Time Sheet.xlsx
+++ b/Baseline_docs/Time Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wskinner\On Drive Files\Git\Secure-Multi-Layer-Network-Project---Capstone\Baseline_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C5830CB-1428-41CC-BA61-283820DCB033}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DA84E80-7965-4ABE-BFC2-C77EFC6EF166}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="17">
   <si>
     <t>Day</t>
   </si>
@@ -666,22 +666,22 @@
       </c>
       <c r="H3" s="1">
         <f>SUM(E:E) + (I3*60) + SUM(D:D)</f>
-        <v>5935</v>
+        <v>6024</v>
       </c>
       <c r="I3" s="6">
         <f>SUM(F:F)</f>
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J3" s="5">
         <f>Table2[[#This Row],[Total Minutes]]/60</f>
-        <v>98.916666666666671</v>
+        <v>100.4</v>
       </c>
       <c r="K3" s="1" t="str">
         <f>IF(Table2[[#This Row],[Hour Percent]] &gt;= Table2[[#This Row],[Hours Needed]], "Hours have been met", "More hours needed")</f>
         <v>More hours needed</v>
       </c>
       <c r="L3" s="1">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="N3" s="1">
         <v>1</v>
@@ -790,11 +790,11 @@
       </c>
       <c r="H6" s="3">
         <f ca="1">NOW()</f>
-        <v>46059.614429398149</v>
+        <v>46062.587746180558</v>
       </c>
       <c r="I6" s="4">
         <f ca="1">NOW()</f>
-        <v>46059.614429398149</v>
+        <v>46062.587746180558</v>
       </c>
       <c r="N6" s="1">
         <v>4</v>
@@ -835,7 +835,7 @@
       </c>
       <c r="O7" s="6">
         <f>SUM(D31:E37) + (60*P7)</f>
-        <v>1313</v>
+        <v>1323</v>
       </c>
       <c r="P7" s="6">
         <f>SUM(F31:F37)</f>
@@ -843,7 +843,7 @@
       </c>
       <c r="Q7" s="5">
         <f t="shared" si="0"/>
-        <v>21.883333333333333</v>
+        <v>22.05</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.35">
@@ -869,15 +869,15 @@
       </c>
       <c r="O8" s="6">
         <f>SUM(D38:E44) + (60*P8)</f>
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="P8" s="6">
         <f>SUM(F38:F44)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.3166666666666667</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.35">
@@ -901,8 +901,14 @@
       <c r="N9" s="1">
         <v>7</v>
       </c>
-      <c r="O9" s="6"/>
-      <c r="P9" s="6"/>
+      <c r="O9" s="6">
+        <f>SUM(D45:E51) + (60*P9)</f>
+        <v>0</v>
+      </c>
+      <c r="P9" s="6">
+        <f>SUM(F45:F51)</f>
+        <v>0</v>
+      </c>
       <c r="Q9" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1423,6 +1429,9 @@
       <c r="C35" s="2">
         <v>46059.61440972222</v>
       </c>
+      <c r="D35" s="5">
+        <v>10</v>
+      </c>
       <c r="E35" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
         <v>26</v>
@@ -1436,8 +1445,12 @@
       <c r="A36" s="7">
         <v>46060</v>
       </c>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
+      <c r="B36" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="E36" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
         <v>0</v>
@@ -1451,8 +1464,12 @@
       <c r="A37" s="7">
         <v>46061</v>
       </c>
-      <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
+      <c r="B37" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="E37" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
         <v>0</v>
@@ -1466,15 +1483,19 @@
       <c r="A38" s="7">
         <v>46062</v>
       </c>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
+      <c r="B38" s="2">
+        <v>46062.532546527778</v>
+      </c>
+      <c r="C38" s="2">
+        <v>46062.587678587966</v>
+      </c>
       <c r="E38" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F38" s="5">
         <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">

--- a/Baseline_docs/Time Sheet.xlsx
+++ b/Baseline_docs/Time Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wskinner\On Drive Files\Git\Secure-Multi-Layer-Network-Project---Capstone\Baseline_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DA84E80-7965-4ABE-BFC2-C77EFC6EF166}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0544F1C7-BD57-4925-A734-8F1F91343B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -790,11 +790,11 @@
       </c>
       <c r="H6" s="3">
         <f ca="1">NOW()</f>
-        <v>46062.587746180558</v>
+        <v>46063.570104629631</v>
       </c>
       <c r="I6" s="4">
         <f ca="1">NOW()</f>
-        <v>46062.587746180558</v>
+        <v>46063.570104629631</v>
       </c>
       <c r="N6" s="1">
         <v>4</v>
@@ -1502,7 +1502,9 @@
       <c r="A39" s="7">
         <v>46063</v>
       </c>
-      <c r="B39" s="2"/>
+      <c r="B39" s="2">
+        <v>46063.570104166669</v>
+      </c>
       <c r="C39" s="2"/>
       <c r="E39" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>

--- a/Baseline_docs/Time Sheet.xlsx
+++ b/Baseline_docs/Time Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wskinner\On Drive Files\Git\Secure-Multi-Layer-Network-Project---Capstone\Baseline_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0544F1C7-BD57-4925-A734-8F1F91343B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19F3C673-9749-405C-90AA-8BEED27F49FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -666,15 +666,15 @@
       </c>
       <c r="H3" s="1">
         <f>SUM(E:E) + (I3*60) + SUM(D:D)</f>
-        <v>6024</v>
+        <v>6221</v>
       </c>
       <c r="I3" s="6">
         <f>SUM(F:F)</f>
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="J3" s="5">
         <f>Table2[[#This Row],[Total Minutes]]/60</f>
-        <v>100.4</v>
+        <v>103.68333333333334</v>
       </c>
       <c r="K3" s="1" t="str">
         <f>IF(Table2[[#This Row],[Hour Percent]] &gt;= Table2[[#This Row],[Hours Needed]], "Hours have been met", "More hours needed")</f>
@@ -790,11 +790,11 @@
       </c>
       <c r="H6" s="3">
         <f ca="1">NOW()</f>
-        <v>46063.570104629631</v>
+        <v>46063.707249537038</v>
       </c>
       <c r="I6" s="4">
         <f ca="1">NOW()</f>
-        <v>46063.570104629631</v>
+        <v>46063.707249537038</v>
       </c>
       <c r="N6" s="1">
         <v>4</v>
@@ -869,15 +869,15 @@
       </c>
       <c r="O8" s="6">
         <f>SUM(D38:E44) + (60*P8)</f>
-        <v>79</v>
+        <v>276</v>
       </c>
       <c r="P8" s="6">
         <f>SUM(F38:F44)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q8" s="5">
         <f t="shared" si="0"/>
-        <v>1.3166666666666667</v>
+        <v>4.5999999999999996</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.35">
@@ -1505,14 +1505,16 @@
       <c r="B39" s="2">
         <v>46063.570104166669</v>
       </c>
-      <c r="C39" s="2"/>
+      <c r="C39" s="2">
+        <v>46063.7071125</v>
+      </c>
       <c r="E39" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F39" s="5">
         <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">

--- a/Baseline_docs/Time Sheet.xlsx
+++ b/Baseline_docs/Time Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wskinner\On Drive Files\Git\Secure-Multi-Layer-Network-Project---Capstone\Baseline_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19F3C673-9749-405C-90AA-8BEED27F49FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E9AE31F-FFB5-412B-84F1-C986B686823E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -666,15 +666,15 @@
       </c>
       <c r="H3" s="1">
         <f>SUM(E:E) + (I3*60) + SUM(D:D)</f>
-        <v>6221</v>
+        <v>6311</v>
       </c>
       <c r="I3" s="6">
         <f>SUM(F:F)</f>
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J3" s="5">
         <f>Table2[[#This Row],[Total Minutes]]/60</f>
-        <v>103.68333333333334</v>
+        <v>105.18333333333334</v>
       </c>
       <c r="K3" s="1" t="str">
         <f>IF(Table2[[#This Row],[Hour Percent]] &gt;= Table2[[#This Row],[Hours Needed]], "Hours have been met", "More hours needed")</f>
@@ -790,11 +790,11 @@
       </c>
       <c r="H6" s="3">
         <f ca="1">NOW()</f>
-        <v>46063.707249537038</v>
+        <v>46064.536971643516</v>
       </c>
       <c r="I6" s="4">
         <f ca="1">NOW()</f>
-        <v>46063.707249537038</v>
+        <v>46064.536971643516</v>
       </c>
       <c r="N6" s="1">
         <v>4</v>
@@ -869,15 +869,15 @@
       </c>
       <c r="O8" s="6">
         <f>SUM(D38:E44) + (60*P8)</f>
-        <v>276</v>
+        <v>366</v>
       </c>
       <c r="P8" s="6">
         <f>SUM(F38:F44)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q8" s="5">
         <f t="shared" si="0"/>
-        <v>4.5999999999999996</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.35">
@@ -1506,22 +1506,24 @@
         <v>46063.570104166669</v>
       </c>
       <c r="C39" s="2">
-        <v>46063.7071125</v>
+        <v>46063.769618055558</v>
       </c>
       <c r="E39" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="F39" s="5">
         <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="7">
         <v>46064</v>
       </c>
-      <c r="B40" s="2"/>
+      <c r="B40" s="2">
+        <v>46064.534594907411</v>
+      </c>
       <c r="C40" s="2"/>
       <c r="E40" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>

--- a/Baseline_docs/Time Sheet.xlsx
+++ b/Baseline_docs/Time Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wskinner\On Drive Files\Git\Secure-Multi-Layer-Network-Project---Capstone\Baseline_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E9AE31F-FFB5-412B-84F1-C986B686823E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{308F260D-AB83-40DE-8AF0-F721DF235C57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -666,15 +666,15 @@
       </c>
       <c r="H3" s="1">
         <f>SUM(E:E) + (I3*60) + SUM(D:D)</f>
-        <v>6311</v>
+        <v>6441</v>
       </c>
       <c r="I3" s="6">
         <f>SUM(F:F)</f>
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="J3" s="5">
         <f>Table2[[#This Row],[Total Minutes]]/60</f>
-        <v>105.18333333333334</v>
+        <v>107.35</v>
       </c>
       <c r="K3" s="1" t="str">
         <f>IF(Table2[[#This Row],[Hour Percent]] &gt;= Table2[[#This Row],[Hours Needed]], "Hours have been met", "More hours needed")</f>
@@ -790,11 +790,11 @@
       </c>
       <c r="H6" s="3">
         <f ca="1">NOW()</f>
-        <v>46064.536971643516</v>
+        <v>46064.601514120368</v>
       </c>
       <c r="I6" s="4">
         <f ca="1">NOW()</f>
-        <v>46064.536971643516</v>
+        <v>46064.601514120368</v>
       </c>
       <c r="N6" s="1">
         <v>4</v>
@@ -869,15 +869,15 @@
       </c>
       <c r="O8" s="6">
         <f>SUM(D38:E44) + (60*P8)</f>
-        <v>366</v>
+        <v>496</v>
       </c>
       <c r="P8" s="6">
         <f>SUM(F38:F44)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q8" s="5">
         <f t="shared" si="0"/>
-        <v>6.1</v>
+        <v>8.2666666666666675</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.35">
@@ -1524,14 +1524,16 @@
       <c r="B40" s="2">
         <v>46064.534594907411</v>
       </c>
-      <c r="C40" s="2"/>
+      <c r="C40" s="2">
+        <v>46064.625451388885</v>
+      </c>
       <c r="E40" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F40" s="5">
         <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">

--- a/Baseline_docs/Time Sheet.xlsx
+++ b/Baseline_docs/Time Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wskinner\On Drive Files\Git\Secure-Multi-Layer-Network-Project---Capstone\Baseline_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{308F260D-AB83-40DE-8AF0-F721DF235C57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{933AF00F-EE7A-41CA-8147-6DB8B1DF3333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -790,11 +790,11 @@
       </c>
       <c r="H6" s="3">
         <f ca="1">NOW()</f>
-        <v>46064.601514120368</v>
+        <v>46065.55529074074</v>
       </c>
       <c r="I6" s="4">
         <f ca="1">NOW()</f>
-        <v>46064.601514120368</v>
+        <v>46065.55529074074</v>
       </c>
       <c r="N6" s="1">
         <v>4</v>
@@ -1540,7 +1540,9 @@
       <c r="A41" s="7">
         <v>46065</v>
       </c>
-      <c r="B41" s="2"/>
+      <c r="B41" s="2">
+        <v>46065.555194328706</v>
+      </c>
       <c r="C41" s="2"/>
       <c r="E41" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>

--- a/Baseline_docs/Time Sheet.xlsx
+++ b/Baseline_docs/Time Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wskinner\On Drive Files\Git\Secure-Multi-Layer-Network-Project---Capstone\Baseline_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{933AF00F-EE7A-41CA-8147-6DB8B1DF3333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3601335-F6F0-417B-9C06-18761DC0C5BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -666,15 +666,15 @@
       </c>
       <c r="H3" s="1">
         <f>SUM(E:E) + (I3*60) + SUM(D:D)</f>
-        <v>6441</v>
+        <v>6714</v>
       </c>
       <c r="I3" s="6">
         <f>SUM(F:F)</f>
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="J3" s="5">
         <f>Table2[[#This Row],[Total Minutes]]/60</f>
-        <v>107.35</v>
+        <v>111.9</v>
       </c>
       <c r="K3" s="1" t="str">
         <f>IF(Table2[[#This Row],[Hour Percent]] &gt;= Table2[[#This Row],[Hours Needed]], "Hours have been met", "More hours needed")</f>
@@ -790,11 +790,11 @@
       </c>
       <c r="H6" s="3">
         <f ca="1">NOW()</f>
-        <v>46065.55529074074</v>
+        <v>46065.745324768519</v>
       </c>
       <c r="I6" s="4">
         <f ca="1">NOW()</f>
-        <v>46065.55529074074</v>
+        <v>46065.745324768519</v>
       </c>
       <c r="N6" s="1">
         <v>4</v>
@@ -869,15 +869,15 @@
       </c>
       <c r="O8" s="6">
         <f>SUM(D38:E44) + (60*P8)</f>
-        <v>496</v>
+        <v>769</v>
       </c>
       <c r="P8" s="6">
         <f>SUM(F38:F44)</f>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="Q8" s="5">
         <f t="shared" si="0"/>
-        <v>8.2666666666666675</v>
+        <v>12.816666666666666</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.35">
@@ -1543,14 +1543,16 @@
       <c r="B41" s="2">
         <v>46065.555194328706</v>
       </c>
-      <c r="C41" s="2"/>
+      <c r="C41" s="2">
+        <v>46065.745251388886</v>
+      </c>
       <c r="E41" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F41" s="5">
         <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">

--- a/Baseline_docs/Time Sheet.xlsx
+++ b/Baseline_docs/Time Sheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wskinner\On Drive Files\Git\Secure-Multi-Layer-Network-Project---Capstone\Baseline_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3601335-F6F0-417B-9C06-18761DC0C5BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6766F61D-7D3E-4DFF-9841-2652E7AAD841}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1900" yWindow="1900" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -666,19 +666,19 @@
       </c>
       <c r="H3" s="1">
         <f>SUM(E:E) + (I3*60) + SUM(D:D)</f>
-        <v>6714</v>
+        <v>7255</v>
       </c>
       <c r="I3" s="6">
         <f>SUM(F:F)</f>
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="J3" s="5">
         <f>Table2[[#This Row],[Total Minutes]]/60</f>
-        <v>111.9</v>
+        <v>120.91666666666667</v>
       </c>
       <c r="K3" s="1" t="str">
         <f>IF(Table2[[#This Row],[Hour Percent]] &gt;= Table2[[#This Row],[Hours Needed]], "Hours have been met", "More hours needed")</f>
-        <v>More hours needed</v>
+        <v>Hours have been met</v>
       </c>
       <c r="L3" s="1">
         <v>120</v>
@@ -790,11 +790,11 @@
       </c>
       <c r="H6" s="3">
         <f ca="1">NOW()</f>
-        <v>46065.745324768519</v>
+        <v>46066.934617708335</v>
       </c>
       <c r="I6" s="4">
         <f ca="1">NOW()</f>
-        <v>46065.745324768519</v>
+        <v>46066.934617708335</v>
       </c>
       <c r="N6" s="1">
         <v>4</v>
@@ -869,15 +869,15 @@
       </c>
       <c r="O8" s="6">
         <f>SUM(D38:E44) + (60*P8)</f>
-        <v>769</v>
+        <v>1310</v>
       </c>
       <c r="P8" s="6">
         <f>SUM(F38:F44)</f>
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="Q8" s="5">
         <f t="shared" si="0"/>
-        <v>12.816666666666666</v>
+        <v>21.833333333333332</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.35">
@@ -1559,15 +1559,22 @@
       <c r="A42" s="7">
         <v>46066</v>
       </c>
-      <c r="B42" s="2"/>
-      <c r="C42" s="2"/>
+      <c r="B42" s="2">
+        <v>46066.568680555552</v>
+      </c>
+      <c r="C42" s="2">
+        <v>46066.934533449072</v>
+      </c>
+      <c r="D42" s="5">
+        <v>15</v>
+      </c>
       <c r="E42" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="F42" s="5">
         <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">

--- a/Baseline_docs/Time Sheet.xlsx
+++ b/Baseline_docs/Time Sheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wskinner\On Drive Files\Git\Secure-Multi-Layer-Network-Project---Capstone\Baseline_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6766F61D-7D3E-4DFF-9841-2652E7AAD841}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C057F4F3-079F-407C-A7ED-684C066A23C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="1900" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="17">
   <si>
     <t>Day</t>
   </si>
@@ -666,15 +666,15 @@
       </c>
       <c r="H3" s="1">
         <f>SUM(E:E) + (I3*60) + SUM(D:D)</f>
-        <v>7255</v>
+        <v>7502</v>
       </c>
       <c r="I3" s="6">
         <f>SUM(F:F)</f>
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="J3" s="5">
         <f>Table2[[#This Row],[Total Minutes]]/60</f>
-        <v>120.91666666666667</v>
+        <v>125.03333333333333</v>
       </c>
       <c r="K3" s="1" t="str">
         <f>IF(Table2[[#This Row],[Hour Percent]] &gt;= Table2[[#This Row],[Hours Needed]], "Hours have been met", "More hours needed")</f>
@@ -790,11 +790,11 @@
       </c>
       <c r="H6" s="3">
         <f ca="1">NOW()</f>
-        <v>46066.934617708335</v>
+        <v>46070.703897916668</v>
       </c>
       <c r="I6" s="4">
         <f ca="1">NOW()</f>
-        <v>46066.934617708335</v>
+        <v>46070.703897916668</v>
       </c>
       <c r="N6" s="1">
         <v>4</v>
@@ -869,15 +869,15 @@
       </c>
       <c r="O8" s="6">
         <f>SUM(D38:E44) + (60*P8)</f>
-        <v>1310</v>
+        <v>1370</v>
       </c>
       <c r="P8" s="6">
         <f>SUM(F38:F44)</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q8" s="5">
         <f t="shared" si="0"/>
-        <v>21.833333333333332</v>
+        <v>22.833333333333332</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.35">
@@ -903,15 +903,15 @@
       </c>
       <c r="O9" s="6">
         <f>SUM(D45:E51) + (60*P9)</f>
-        <v>0</v>
+        <v>187</v>
       </c>
       <c r="P9" s="6">
         <f>SUM(F45:F51)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q9" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3.1166666666666667</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.35">
@@ -1563,7 +1563,7 @@
         <v>46066.568680555552</v>
       </c>
       <c r="C42" s="2">
-        <v>46066.934533449072</v>
+        <v>46066.976203703707</v>
       </c>
       <c r="D42" s="5">
         <v>15</v>
@@ -1574,15 +1574,19 @@
       </c>
       <c r="F42" s="5">
         <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="7">
         <v>46067</v>
       </c>
-      <c r="B43" s="2"/>
-      <c r="C43" s="2"/>
+      <c r="B43" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="E43" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
         <v>0</v>
@@ -1596,8 +1600,12 @@
       <c r="A44" s="7">
         <v>46068</v>
       </c>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
+      <c r="B44" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="E44" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
         <v>0</v>
@@ -1611,8 +1619,12 @@
       <c r="A45" s="7">
         <v>46069</v>
       </c>
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
+      <c r="B45" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="E45" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
         <v>0</v>
@@ -1626,15 +1638,19 @@
       <c r="A46" s="7">
         <v>46070</v>
       </c>
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
+      <c r="B46" s="2">
+        <v>46070.578633564815</v>
+      </c>
+      <c r="C46" s="2">
+        <v>46070.708599537036</v>
+      </c>
       <c r="E46" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F46" s="5">
         <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.35">

--- a/Baseline_docs/Time Sheet.xlsx
+++ b/Baseline_docs/Time Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wskinner\On Drive Files\Git\Secure-Multi-Layer-Network-Project---Capstone\Baseline_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C057F4F3-079F-407C-A7ED-684C066A23C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75EA89F1-B753-4CFD-BDB7-D729D01B9077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="17">
   <si>
     <t>Day</t>
   </si>
@@ -665,23 +665,23 @@
         <v>1</v>
       </c>
       <c r="H3" s="1">
-        <f>SUM(E:E) + (I3*60) + SUM(D:D)</f>
-        <v>7502</v>
+        <f ca="1">SUM(E:E) + (I3*60) + SUM(D:D)</f>
+        <v>7685</v>
       </c>
       <c r="I3" s="6">
-        <f>SUM(F:F)</f>
-        <v>113</v>
+        <f ca="1">SUM(F:F)</f>
+        <v>115</v>
       </c>
       <c r="J3" s="5">
-        <f>Table2[[#This Row],[Total Minutes]]/60</f>
-        <v>125.03333333333333</v>
+        <f ca="1">Table2[[#This Row],[Total Minutes]]/60</f>
+        <v>128.08333333333334</v>
       </c>
       <c r="K3" s="1" t="str">
-        <f>IF(Table2[[#This Row],[Hour Percent]] &gt;= Table2[[#This Row],[Hours Needed]], "Hours have been met", "More hours needed")</f>
-        <v>Hours have been met</v>
+        <f ca="1">IF(Table2[[#This Row],[Hour Percent]] &gt;= Table2[[#This Row],[Hours Needed]], "Hours have been met", "More hours needed")</f>
+        <v>More hours needed</v>
       </c>
       <c r="L3" s="1">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="N3" s="1">
         <v>1</v>
@@ -790,11 +790,11 @@
       </c>
       <c r="H6" s="3">
         <f ca="1">NOW()</f>
-        <v>46070.703897916668</v>
+        <v>46072.710983680554</v>
       </c>
       <c r="I6" s="4">
         <f ca="1">NOW()</f>
-        <v>46070.703897916668</v>
+        <v>46072.710983680554</v>
       </c>
       <c r="N6" s="1">
         <v>4</v>
@@ -902,16 +902,16 @@
         <v>7</v>
       </c>
       <c r="O9" s="6">
-        <f>SUM(D45:E51) + (60*P9)</f>
-        <v>187</v>
+        <f ca="1">SUM(D45:E51) + (60*P9)</f>
+        <v>370</v>
       </c>
       <c r="P9" s="6">
-        <f>SUM(F45:F51)</f>
-        <v>3</v>
+        <f ca="1">SUM(F45:F51)</f>
+        <v>5</v>
       </c>
       <c r="Q9" s="5">
-        <f t="shared" si="0"/>
-        <v>3.1166666666666667</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>6.166666666666667</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.35">
@@ -1657,8 +1657,15 @@
       <c r="A47" s="7">
         <v>46071</v>
       </c>
-      <c r="B47" s="2"/>
-      <c r="C47" s="2"/>
+      <c r="B47" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D47" s="5">
+        <v>60</v>
+      </c>
       <c r="E47" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
         <v>0</v>
@@ -1672,15 +1679,20 @@
       <c r="A48" s="7">
         <v>46072</v>
       </c>
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
+      <c r="B48" s="2">
+        <v>46072.625451388885</v>
+      </c>
+      <c r="C48" s="4">
+        <f ca="1">NOW()</f>
+        <v>46072.710983680554</v>
+      </c>
       <c r="E48" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
+        <f ca="1">IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>3</v>
       </c>
       <c r="F48" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
+        <f ca="1">IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">

--- a/Baseline_docs/Time Sheet.xlsx
+++ b/Baseline_docs/Time Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wskinner\On Drive Files\Git\Secure-Multi-Layer-Network-Project---Capstone\Baseline_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75EA89F1-B753-4CFD-BDB7-D729D01B9077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40D86B45-5A49-4B01-9020-B604B44B7D9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="17">
   <si>
     <t>Day</t>
   </si>
@@ -665,20 +665,20 @@
         <v>1</v>
       </c>
       <c r="H3" s="1">
-        <f ca="1">SUM(E:E) + (I3*60) + SUM(D:D)</f>
-        <v>7685</v>
+        <f>SUM(E:E) + (I3*60) + SUM(D:D)</f>
+        <v>8693</v>
       </c>
       <c r="I3" s="6">
-        <f ca="1">SUM(F:F)</f>
-        <v>115</v>
+        <f>SUM(F:F)</f>
+        <v>130</v>
       </c>
       <c r="J3" s="5">
-        <f ca="1">Table2[[#This Row],[Total Minutes]]/60</f>
-        <v>128.08333333333334</v>
+        <f>Table2[[#This Row],[Total Minutes]]/60</f>
+        <v>144.88333333333333</v>
       </c>
       <c r="K3" s="1" t="str">
-        <f ca="1">IF(Table2[[#This Row],[Hour Percent]] &gt;= Table2[[#This Row],[Hours Needed]], "Hours have been met", "More hours needed")</f>
-        <v>More hours needed</v>
+        <f>IF(Table2[[#This Row],[Hour Percent]] &gt;= Table2[[#This Row],[Hours Needed]], "Hours have been met", "More hours needed")</f>
+        <v>Hours have been met</v>
       </c>
       <c r="L3" s="1">
         <v>140</v>
@@ -790,11 +790,11 @@
       </c>
       <c r="H6" s="3">
         <f ca="1">NOW()</f>
-        <v>46072.710983680554</v>
+        <v>46076.503019675925</v>
       </c>
       <c r="I6" s="4">
         <f ca="1">NOW()</f>
-        <v>46072.710983680554</v>
+        <v>46076.503019675925</v>
       </c>
       <c r="N6" s="1">
         <v>4</v>
@@ -902,16 +902,16 @@
         <v>7</v>
       </c>
       <c r="O9" s="6">
-        <f ca="1">SUM(D45:E51) + (60*P9)</f>
-        <v>370</v>
+        <f>SUM(D45:E51) + (60*P9)</f>
+        <v>1378</v>
       </c>
       <c r="P9" s="6">
-        <f ca="1">SUM(F45:F51)</f>
-        <v>5</v>
+        <f>SUM(F45:F51)</f>
+        <v>20</v>
       </c>
       <c r="Q9" s="5">
-        <f t="shared" ca="1" si="0"/>
-        <v>6.166666666666667</v>
+        <f t="shared" si="0"/>
+        <v>22.966666666666665</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.35">
@@ -935,8 +935,14 @@
       <c r="N10" s="1">
         <v>8</v>
       </c>
-      <c r="O10" s="6"/>
-      <c r="P10" s="6"/>
+      <c r="O10" s="6">
+        <f>SUM(D52:E58) + (60*P10)</f>
+        <v>0</v>
+      </c>
+      <c r="P10" s="6">
+        <f>SUM(F52:F58)</f>
+        <v>0</v>
+      </c>
       <c r="Q10" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1682,16 +1688,15 @@
       <c r="B48" s="2">
         <v>46072.625451388885</v>
       </c>
-      <c r="C48" s="4">
-        <f ca="1">NOW()</f>
-        <v>46072.710983680554</v>
+      <c r="C48" s="2">
+        <v>46072.729618055557</v>
       </c>
       <c r="E48" s="5">
-        <f ca="1">IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>3</v>
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>30</v>
       </c>
       <c r="F48" s="5">
-        <f ca="1">IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
         <v>2</v>
       </c>
     </row>
@@ -1699,23 +1704,34 @@
       <c r="A49" s="7">
         <v>46073</v>
       </c>
-      <c r="B49" s="2"/>
-      <c r="C49" s="2"/>
+      <c r="B49" s="2">
+        <v>46073.472314814811</v>
+      </c>
+      <c r="C49" s="2">
+        <v>46074.125613425924</v>
+      </c>
+      <c r="D49" s="5">
+        <v>10</v>
+      </c>
       <c r="E49" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F49" s="5">
         <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="7">
         <v>46074</v>
       </c>
-      <c r="B50" s="2"/>
-      <c r="C50" s="2"/>
+      <c r="B50" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="E50" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
         <v>0</v>
@@ -1729,11 +1745,15 @@
       <c r="A51" s="7">
         <v>46075</v>
       </c>
-      <c r="B51" s="2"/>
-      <c r="C51" s="2"/>
+      <c r="B51" s="2">
+        <v>46075.661360416663</v>
+      </c>
+      <c r="C51" s="2">
+        <v>46075.683182870373</v>
+      </c>
       <c r="E51" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F51" s="5">
         <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
@@ -1744,7 +1764,9 @@
       <c r="A52" s="7">
         <v>46076</v>
       </c>
-      <c r="B52" s="2"/>
+      <c r="B52" s="2">
+        <v>46076.986793981479</v>
+      </c>
       <c r="C52" s="2"/>
       <c r="E52" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>

--- a/Baseline_docs/Time Sheet.xlsx
+++ b/Baseline_docs/Time Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wskinner\On Drive Files\Git\Secure-Multi-Layer-Network-Project---Capstone\Baseline_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40D86B45-5A49-4B01-9020-B604B44B7D9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B18D4D08-B3D2-4AD3-9296-60D765AF56B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -666,15 +666,15 @@
       </c>
       <c r="H3" s="1">
         <f>SUM(E:E) + (I3*60) + SUM(D:D)</f>
-        <v>8693</v>
+        <v>8937</v>
       </c>
       <c r="I3" s="6">
         <f>SUM(F:F)</f>
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="J3" s="5">
         <f>Table2[[#This Row],[Total Minutes]]/60</f>
-        <v>144.88333333333333</v>
+        <v>148.94999999999999</v>
       </c>
       <c r="K3" s="1" t="str">
         <f>IF(Table2[[#This Row],[Hour Percent]] &gt;= Table2[[#This Row],[Hours Needed]], "Hours have been met", "More hours needed")</f>
@@ -790,11 +790,11 @@
       </c>
       <c r="H6" s="3">
         <f ca="1">NOW()</f>
-        <v>46076.503019675925</v>
+        <v>46076.657140162039</v>
       </c>
       <c r="I6" s="4">
         <f ca="1">NOW()</f>
-        <v>46076.503019675925</v>
+        <v>46076.657140162039</v>
       </c>
       <c r="N6" s="1">
         <v>4</v>
@@ -937,15 +937,15 @@
       </c>
       <c r="O10" s="6">
         <f>SUM(D52:E58) + (60*P10)</f>
-        <v>0</v>
+        <v>244</v>
       </c>
       <c r="P10" s="6">
         <f>SUM(F52:F58)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q10" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4.0666666666666664</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.35">
@@ -1765,16 +1765,18 @@
         <v>46076</v>
       </c>
       <c r="B52" s="2">
-        <v>46076.986793981479</v>
-      </c>
-      <c r="C52" s="2"/>
+        <v>46076.486793981479</v>
+      </c>
+      <c r="C52" s="2">
+        <v>46076.656846874997</v>
+      </c>
       <c r="E52" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F52" s="5">
         <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">

--- a/Baseline_docs/Time Sheet.xlsx
+++ b/Baseline_docs/Time Sheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wskinner\On Drive Files\Git\Secure-Multi-Layer-Network-Project---Capstone\Baseline_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B18D4D08-B3D2-4AD3-9296-60D765AF56B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B20A4F0-1017-4C55-8CF9-D1FD0E043843}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3420" yWindow="3420" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -665,23 +665,23 @@
         <v>1</v>
       </c>
       <c r="H3" s="1">
-        <f>SUM(E:E) + (I3*60) + SUM(D:D)</f>
-        <v>8937</v>
+        <f ca="1">SUM(E:E) + (I3*60) + SUM(D:D)</f>
+        <v>9863</v>
       </c>
       <c r="I3" s="6">
-        <f>SUM(F:F)</f>
-        <v>134</v>
+        <f ca="1">SUM(F:F)</f>
+        <v>148</v>
       </c>
       <c r="J3" s="5">
-        <f>Table2[[#This Row],[Total Minutes]]/60</f>
-        <v>148.94999999999999</v>
+        <f ca="1">Table2[[#This Row],[Total Minutes]]/60</f>
+        <v>164.38333333333333</v>
       </c>
       <c r="K3" s="1" t="str">
-        <f>IF(Table2[[#This Row],[Hour Percent]] &gt;= Table2[[#This Row],[Hours Needed]], "Hours have been met", "More hours needed")</f>
-        <v>Hours have been met</v>
+        <f ca="1">IF(Table2[[#This Row],[Hour Percent]] &gt;= Table2[[#This Row],[Hours Needed]], "Hours have been met", "More hours needed")</f>
+        <v>More hours needed</v>
       </c>
       <c r="L3" s="1">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="N3" s="1">
         <v>1</v>
@@ -790,11 +790,11 @@
       </c>
       <c r="H6" s="3">
         <f ca="1">NOW()</f>
-        <v>46076.657140162039</v>
+        <v>46078.502825347219</v>
       </c>
       <c r="I6" s="4">
         <f ca="1">NOW()</f>
-        <v>46076.657140162039</v>
+        <v>46078.502825347219</v>
       </c>
       <c r="N6" s="1">
         <v>4</v>
@@ -936,16 +936,16 @@
         <v>8</v>
       </c>
       <c r="O10" s="6">
-        <f>SUM(D52:E58) + (60*P10)</f>
-        <v>244</v>
+        <f ca="1">SUM(D52:E58) + (60*P10)</f>
+        <v>1170</v>
       </c>
       <c r="P10" s="6">
-        <f>SUM(F52:F58)</f>
-        <v>4</v>
+        <f ca="1">SUM(F52:F58)</f>
+        <v>18</v>
       </c>
       <c r="Q10" s="5">
-        <f t="shared" si="0"/>
-        <v>4.0666666666666664</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>19.5</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.35">
@@ -1783,29 +1783,38 @@
       <c r="A53" s="7">
         <v>46077</v>
       </c>
-      <c r="B53" s="2"/>
-      <c r="C53" s="2"/>
+      <c r="B53" s="4">
+        <v>46077.555694444447</v>
+      </c>
+      <c r="C53" s="4">
+        <v>46078.167118055557</v>
+      </c>
       <c r="E53" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F53" s="5">
         <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" s="7">
         <v>46078</v>
       </c>
-      <c r="B54" s="2"/>
-      <c r="C54" s="2"/>
+      <c r="B54" s="2">
+        <v>46078.470724305553</v>
+      </c>
+      <c r="C54" s="4">
+        <f ca="1">NOW()</f>
+        <v>46078.502825347219</v>
+      </c>
       <c r="E54" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
+        <f ca="1">IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>46</v>
       </c>
       <c r="F54" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <f ca="1">IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
         <v>0</v>
       </c>
     </row>

--- a/Baseline_docs/Time Sheet.xlsx
+++ b/Baseline_docs/Time Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wskinner\On Drive Files\Git\Secure-Multi-Layer-Network-Project---Capstone\Baseline_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B20A4F0-1017-4C55-8CF9-D1FD0E043843}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{887C2E37-072C-4740-87EE-4A40D30CC4A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3420" yWindow="3420" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="17">
   <si>
     <t>Day</t>
   </si>
@@ -665,23 +665,23 @@
         <v>1</v>
       </c>
       <c r="H3" s="1">
-        <f ca="1">SUM(E:E) + (I3*60) + SUM(D:D)</f>
-        <v>9863</v>
+        <f>SUM(E:E) + (I3*60) + SUM(D:D)</f>
+        <v>10550</v>
       </c>
       <c r="I3" s="6">
-        <f ca="1">SUM(F:F)</f>
-        <v>148</v>
+        <f>SUM(F:F)</f>
+        <v>158</v>
       </c>
       <c r="J3" s="5">
-        <f ca="1">Table2[[#This Row],[Total Minutes]]/60</f>
-        <v>164.38333333333333</v>
+        <f>Table2[[#This Row],[Total Minutes]]/60</f>
+        <v>175.83333333333334</v>
       </c>
       <c r="K3" s="1" t="str">
-        <f ca="1">IF(Table2[[#This Row],[Hour Percent]] &gt;= Table2[[#This Row],[Hours Needed]], "Hours have been met", "More hours needed")</f>
+        <f>IF(Table2[[#This Row],[Hour Percent]] &gt;= Table2[[#This Row],[Hours Needed]], "Hours have been met", "More hours needed")</f>
         <v>More hours needed</v>
       </c>
       <c r="L3" s="1">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="N3" s="1">
         <v>1</v>
@@ -790,11 +790,11 @@
       </c>
       <c r="H6" s="3">
         <f ca="1">NOW()</f>
-        <v>46078.502825347219</v>
+        <v>46080.607441550928</v>
       </c>
       <c r="I6" s="4">
         <f ca="1">NOW()</f>
-        <v>46078.502825347219</v>
+        <v>46080.607441550928</v>
       </c>
       <c r="N6" s="1">
         <v>4</v>
@@ -936,16 +936,16 @@
         <v>8</v>
       </c>
       <c r="O10" s="6">
-        <f ca="1">SUM(D52:E58) + (60*P10)</f>
-        <v>1170</v>
+        <f>SUM(D52:E58) + (60*P10)</f>
+        <v>1857</v>
       </c>
       <c r="P10" s="6">
-        <f ca="1">SUM(F52:F58)</f>
-        <v>18</v>
+        <f>SUM(F52:F58)</f>
+        <v>28</v>
       </c>
       <c r="Q10" s="5">
-        <f t="shared" ca="1" si="0"/>
-        <v>19.5</v>
+        <f t="shared" si="0"/>
+        <v>30.95</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.35">
@@ -969,8 +969,14 @@
       <c r="N11" s="1">
         <v>9</v>
       </c>
-      <c r="O11" s="6"/>
-      <c r="P11" s="6"/>
+      <c r="O11" s="6">
+        <f>SUM(D59:E65) + (60*P11)</f>
+        <v>0</v>
+      </c>
+      <c r="P11" s="6">
+        <f>SUM(F59:F65)</f>
+        <v>0</v>
+      </c>
       <c r="Q11" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1805,43 +1811,50 @@
       <c r="B54" s="2">
         <v>46078.470724305553</v>
       </c>
-      <c r="C54" s="4">
-        <f ca="1">NOW()</f>
-        <v>46078.502825347219</v>
+      <c r="C54" s="2">
+        <v>46078.542256944442</v>
       </c>
       <c r="E54" s="5">
-        <f ca="1">IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>46</v>
+        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
+        <v>43</v>
       </c>
       <c r="F54" s="5">
-        <f ca="1">IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
+        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" s="7">
         <v>46079</v>
       </c>
-      <c r="B55" s="2"/>
-      <c r="C55" s="2"/>
+      <c r="B55" s="2">
+        <v>46079.585710995372</v>
+      </c>
+      <c r="C55" s="2">
+        <v>46079.999594907407</v>
+      </c>
       <c r="E55" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F55" s="5">
         <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" s="7">
         <v>46080</v>
       </c>
-      <c r="B56" s="2"/>
-      <c r="C56" s="2"/>
+      <c r="B56" s="4">
+        <v>46080.583541666667</v>
+      </c>
+      <c r="C56" s="2">
+        <v>46080.607357291665</v>
+      </c>
       <c r="E56" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F56" s="5">
         <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
@@ -1852,8 +1865,12 @@
       <c r="A57" s="7">
         <v>46081</v>
       </c>
-      <c r="B57" s="2"/>
-      <c r="C57" s="2"/>
+      <c r="B57" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="E57" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
         <v>0</v>
@@ -1867,8 +1884,12 @@
       <c r="A58" s="7">
         <v>46082</v>
       </c>
-      <c r="B58" s="2"/>
-      <c r="C58" s="2"/>
+      <c r="B58" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="E58" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
         <v>0</v>

--- a/Baseline_docs/Time Sheet.xlsx
+++ b/Baseline_docs/Time Sheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wskinner\On Drive Files\Git\Secure-Multi-Layer-Network-Project---Capstone\Baseline_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{887C2E37-072C-4740-87EE-4A40D30CC4A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{947B0467-19A7-484B-AA9C-96B4D21462BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="3420" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -250,8 +250,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AECFD94D-BC69-43FE-8A1B-A8548D9C1CB8}" name="Table1" displayName="Table1" ref="A2:F75" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
-  <autoFilter ref="A2:F75" xr:uid="{AECFD94D-BC69-43FE-8A1B-A8548D9C1CB8}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AECFD94D-BC69-43FE-8A1B-A8548D9C1CB8}" name="Table1" displayName="Table1" ref="A2:F72" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
+  <autoFilter ref="A2:F72" xr:uid="{AECFD94D-BC69-43FE-8A1B-A8548D9C1CB8}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{7D80F612-B207-4202-A1B2-4CDD0B31BE04}" name="Day" dataDxfId="18"/>
     <tableColumn id="2" xr3:uid="{809082CE-E596-42B5-B407-A4E321ECCB56}" name="Start" dataDxfId="17"/>
@@ -568,7 +568,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q75"/>
+  <dimension ref="A1:Q72"/>
   <sheetFormatPr defaultColWidth="13.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="3" width="13.81640625" style="1"/>
@@ -666,15 +666,15 @@
       </c>
       <c r="H3" s="1">
         <f>SUM(E:E) + (I3*60) + SUM(D:D)</f>
-        <v>10550</v>
+        <v>11009</v>
       </c>
       <c r="I3" s="6">
         <f>SUM(F:F)</f>
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="J3" s="5">
         <f>Table2[[#This Row],[Total Minutes]]/60</f>
-        <v>175.83333333333334</v>
+        <v>183.48333333333332</v>
       </c>
       <c r="K3" s="1" t="str">
         <f>IF(Table2[[#This Row],[Hour Percent]] &gt;= Table2[[#This Row],[Hours Needed]], "Hours have been met", "More hours needed")</f>
@@ -790,11 +790,11 @@
       </c>
       <c r="H6" s="3">
         <f ca="1">NOW()</f>
-        <v>46080.607441550928</v>
+        <v>46084.619718402777</v>
       </c>
       <c r="I6" s="4">
         <f ca="1">NOW()</f>
-        <v>46080.607441550928</v>
+        <v>46084.619718402777</v>
       </c>
       <c r="N6" s="1">
         <v>4</v>
@@ -971,15 +971,15 @@
       </c>
       <c r="O11" s="6">
         <f>SUM(D59:E65) + (60*P11)</f>
-        <v>0</v>
+        <v>459</v>
       </c>
       <c r="P11" s="6">
         <f>SUM(F59:F65)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q11" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>7.65</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.35">
@@ -1003,8 +1003,14 @@
       <c r="N12" s="1">
         <v>10</v>
       </c>
-      <c r="O12" s="6"/>
-      <c r="P12" s="6"/>
+      <c r="O12" s="6">
+        <f>SUM(D66:E72) + (60*P12)</f>
+        <v>0</v>
+      </c>
+      <c r="P12" s="6">
+        <f>SUM(F66:F72)</f>
+        <v>0</v>
+      </c>
       <c r="Q12" s="5">
         <f>O12/60</f>
         <v>0</v>
@@ -1903,30 +1909,41 @@
       <c r="A59" s="7">
         <v>46083</v>
       </c>
-      <c r="B59" s="2"/>
-      <c r="C59" s="2"/>
+      <c r="B59" s="4">
+        <v>46083.590872106484</v>
+      </c>
+      <c r="C59" s="4">
+        <v>46083.715868055559</v>
+      </c>
+      <c r="D59" s="5">
+        <v>30</v>
+      </c>
       <c r="E59" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
         <v>0</v>
       </c>
       <c r="F59" s="5">
         <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" s="7">
         <v>46084</v>
       </c>
-      <c r="B60" s="2"/>
-      <c r="C60" s="2"/>
+      <c r="B60" s="4">
+        <v>46084.619406018515</v>
+      </c>
+      <c r="C60" s="4">
+        <v>46084.792326388888</v>
+      </c>
       <c r="E60" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F60" s="5">
         <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.35">
@@ -2105,51 +2122,6 @@
         <v>0</v>
       </c>
       <c r="F72" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A73" s="7">
-        <v>46097</v>
-      </c>
-      <c r="B73" s="2"/>
-      <c r="C73" s="2"/>
-      <c r="E73" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
-      <c r="F73" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A74" s="7">
-        <v>46098</v>
-      </c>
-      <c r="B74" s="2"/>
-      <c r="C74" s="2"/>
-      <c r="E74" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
-      <c r="F74" s="5">
-        <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A75" s="7">
-        <v>46099</v>
-      </c>
-      <c r="B75" s="2"/>
-      <c r="C75" s="2"/>
-      <c r="E75" s="5">
-        <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
-      </c>
-      <c r="F75" s="5">
         <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
         <v>0</v>
       </c>

--- a/Baseline_docs/Time Sheet.xlsx
+++ b/Baseline_docs/Time Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wskinner\On Drive Files\Git\Secure-Multi-Layer-Network-Project---Capstone\Baseline_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{947B0467-19A7-484B-AA9C-96B4D21462BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{491844DF-AF04-4D69-9F30-311CD43A7DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,6 +33,28 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -161,7 +183,25 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="21">
+  <dxfs count="26">
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -250,17 +290,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AECFD94D-BC69-43FE-8A1B-A8548D9C1CB8}" name="Table1" displayName="Table1" ref="A2:F72" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AECFD94D-BC69-43FE-8A1B-A8548D9C1CB8}" name="Table1" displayName="Table1" ref="A2:F72" totalsRowShown="0" headerRowDxfId="25" dataDxfId="24">
   <autoFilter ref="A2:F72" xr:uid="{AECFD94D-BC69-43FE-8A1B-A8548D9C1CB8}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{7D80F612-B207-4202-A1B2-4CDD0B31BE04}" name="Day" dataDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{809082CE-E596-42B5-B407-A4E321ECCB56}" name="Start" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{387E5ED8-33C5-4EC7-A1F3-CE1B1DDAF190}" name="Stop" dataDxfId="16"/>
-    <tableColumn id="6" xr3:uid="{F560E705-D838-45AE-BE0C-270C69667AC2}" name="Extra Mins" dataDxfId="15"/>
-    <tableColumn id="4" xr3:uid="{A72F3DB0-D92C-4679-A812-253243311EF0}" name="Minutes " dataDxfId="14">
+    <tableColumn id="1" xr3:uid="{7D80F612-B207-4202-A1B2-4CDD0B31BE04}" name="Day" dataDxfId="23"/>
+    <tableColumn id="2" xr3:uid="{809082CE-E596-42B5-B407-A4E321ECCB56}" name="Start" dataDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{387E5ED8-33C5-4EC7-A1F3-CE1B1DDAF190}" name="Stop" dataDxfId="21"/>
+    <tableColumn id="6" xr3:uid="{F560E705-D838-45AE-BE0C-270C69667AC2}" name="Extra Mins" dataDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{A72F3DB0-D92C-4679-A812-253243311EF0}" name="Minutes " dataDxfId="19">
       <calculatedColumnFormula>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{CE4B143E-B608-48C4-8FCC-14B01E692DCB}" name="Hours" dataDxfId="13">
+    <tableColumn id="5" xr3:uid="{CE4B143E-B608-48C4-8FCC-14B01E692DCB}" name="Hours" dataDxfId="18">
       <calculatedColumnFormula>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -269,35 +309,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{BCDE2B7C-F4D9-498C-BDF8-E77B124E5F78}" name="Table2" displayName="Table2" ref="H2:L3" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{BCDE2B7C-F4D9-498C-BDF8-E77B124E5F78}" name="Table2" displayName="Table2" ref="H2:L4" totalsRowCount="1" headerRowDxfId="17" dataDxfId="16">
   <autoFilter ref="H2:L3" xr:uid="{BCDE2B7C-F4D9-498C-BDF8-E77B124E5F78}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{25609316-2FC7-4598-9816-D773B5ABDED5}" name="Total Minutes" dataDxfId="10">
+    <tableColumn id="1" xr3:uid="{25609316-2FC7-4598-9816-D773B5ABDED5}" name="Total Minutes" dataDxfId="15" totalsRowDxfId="4">
       <calculatedColumnFormula>SUM(E:E) + (I3*60) + SUM(D:D)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C48BBBC8-9BDB-469A-A714-B3361A5491E0}" name="Total Hours" dataDxfId="9">
+    <tableColumn id="2" xr3:uid="{C48BBBC8-9BDB-469A-A714-B3361A5491E0}" name="Total Hours" dataDxfId="14" totalsRowDxfId="3">
       <calculatedColumnFormula>SUM(F:F)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{B3EDE8C1-FEE6-4401-BAF1-7A6A74F4FE86}" name="Hour Percent" dataDxfId="8">
+    <tableColumn id="3" xr3:uid="{B3EDE8C1-FEE6-4401-BAF1-7A6A74F4FE86}" name="Hour Percent" dataDxfId="13" totalsRowDxfId="2">
       <calculatedColumnFormula>Table2[[#This Row],[Total Minutes]]/60</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{8FB2D23B-72D8-4504-BE1A-A47C565D5166}" name="Hours Met" dataDxfId="7">
+    <tableColumn id="4" xr3:uid="{8FB2D23B-72D8-4504-BE1A-A47C565D5166}" name="Hours Met" totalsRowFunction="custom" dataDxfId="12" totalsRowDxfId="1">
       <calculatedColumnFormula>IF(Table2[[#This Row],[Hour Percent]] &gt;= Table2[[#This Row],[Hours Needed]], "Hours have been met", "More hours needed")</calculatedColumnFormula>
+      <totalsRowFormula array="1">Table2[Hours Needed]-Table2[Hour Percent]</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{643AEBD5-F2A2-4877-923F-2A6F10830FA5}" name="Hours Needed" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{643AEBD5-F2A2-4877-923F-2A6F10830FA5}" name="Hours Needed" dataDxfId="11" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{0B533ACD-D878-47CD-A04A-12CDF739F4F4}" name="Table3" displayName="Table3" ref="N2:Q12" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{0B533ACD-D878-47CD-A04A-12CDF739F4F4}" name="Table3" displayName="Table3" ref="N2:Q12" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
   <autoFilter ref="N2:Q12" xr:uid="{0B533ACD-D878-47CD-A04A-12CDF739F4F4}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{CFA6B21D-D050-4C14-8F9A-5D7117BEA113}" name="Weeks" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{1CA91632-7336-422D-ABF9-C5E3F08EFBA5}" name="Minutes" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{BB9EBBBA-CBEE-4ACF-8769-1D581F89C8FE}" name="Hours" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{8911D862-F455-4BFD-BDFF-6839D678C8CE}" name="Hour %" dataDxfId="0">
+    <tableColumn id="1" xr3:uid="{CFA6B21D-D050-4C14-8F9A-5D7117BEA113}" name="Weeks" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{1CA91632-7336-422D-ABF9-C5E3F08EFBA5}" name="Minutes" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{BB9EBBBA-CBEE-4ACF-8769-1D581F89C8FE}" name="Hours" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{8911D862-F455-4BFD-BDFF-6839D678C8CE}" name="Hour %" dataDxfId="5">
       <calculatedColumnFormula>O3/60</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -666,15 +707,15 @@
       </c>
       <c r="H3" s="1">
         <f>SUM(E:E) + (I3*60) + SUM(D:D)</f>
-        <v>11009</v>
+        <v>11374</v>
       </c>
       <c r="I3" s="6">
         <f>SUM(F:F)</f>
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="J3" s="5">
         <f>Table2[[#This Row],[Total Minutes]]/60</f>
-        <v>183.48333333333332</v>
+        <v>189.56666666666666</v>
       </c>
       <c r="K3" s="1" t="str">
         <f>IF(Table2[[#This Row],[Hour Percent]] &gt;= Table2[[#This Row],[Hours Needed]], "Hours have been met", "More hours needed")</f>
@@ -717,6 +758,12 @@
         <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
         <v>2</v>
       </c>
+      <c r="I4" s="6"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5" cm="1">
+        <f t="array" ref="K4">Table2[Hours Needed]-Table2[Hour Percent]</f>
+        <v>10.433333333333337</v>
+      </c>
       <c r="N4" s="1">
         <v>2</v>
       </c>
@@ -790,11 +837,11 @@
       </c>
       <c r="H6" s="3">
         <f ca="1">NOW()</f>
-        <v>46084.619718402777</v>
+        <v>46085.575433101854</v>
       </c>
       <c r="I6" s="4">
         <f ca="1">NOW()</f>
-        <v>46084.619718402777</v>
+        <v>46085.575433101854</v>
       </c>
       <c r="N6" s="1">
         <v>4</v>
@@ -971,15 +1018,15 @@
       </c>
       <c r="O11" s="6">
         <f>SUM(D59:E65) + (60*P11)</f>
-        <v>459</v>
+        <v>824</v>
       </c>
       <c r="P11" s="6">
         <f>SUM(F59:F65)</f>
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="Q11" s="5">
         <f t="shared" si="0"/>
-        <v>7.65</v>
+        <v>13.733333333333333</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.35">
@@ -1935,7 +1982,7 @@
         <v>46084.619406018515</v>
       </c>
       <c r="C60" s="4">
-        <v>46084.792326388888</v>
+        <v>46085.042326388888</v>
       </c>
       <c r="E60" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
@@ -1943,15 +1990,20 @@
       </c>
       <c r="F60" s="5">
         <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" s="7">
         <v>46085</v>
       </c>
-      <c r="B61" s="2"/>
+      <c r="B61" s="2">
+        <v>46085.573803009262</v>
+      </c>
       <c r="C61" s="2"/>
+      <c r="D61" s="5">
+        <v>5</v>
+      </c>
       <c r="E61" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
         <v>0</v>

--- a/Baseline_docs/Time Sheet.xlsx
+++ b/Baseline_docs/Time Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wskinner\On Drive Files\Git\Secure-Multi-Layer-Network-Project---Capstone\Baseline_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{491844DF-AF04-4D69-9F30-311CD43A7DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EB38C69-F4D6-4EC5-8EE8-C998D3C11772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -185,56 +185,56 @@
   </cellStyles>
   <dxfs count="26">
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -312,33 +312,33 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{BCDE2B7C-F4D9-498C-BDF8-E77B124E5F78}" name="Table2" displayName="Table2" ref="H2:L4" totalsRowCount="1" headerRowDxfId="17" dataDxfId="16">
   <autoFilter ref="H2:L3" xr:uid="{BCDE2B7C-F4D9-498C-BDF8-E77B124E5F78}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{25609316-2FC7-4598-9816-D773B5ABDED5}" name="Total Minutes" dataDxfId="15" totalsRowDxfId="4">
+    <tableColumn id="1" xr3:uid="{25609316-2FC7-4598-9816-D773B5ABDED5}" name="Total Minutes" dataDxfId="15" totalsRowDxfId="14">
       <calculatedColumnFormula>SUM(E:E) + (I3*60) + SUM(D:D)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C48BBBC8-9BDB-469A-A714-B3361A5491E0}" name="Total Hours" dataDxfId="14" totalsRowDxfId="3">
+    <tableColumn id="2" xr3:uid="{C48BBBC8-9BDB-469A-A714-B3361A5491E0}" name="Total Hours" dataDxfId="13" totalsRowDxfId="12">
       <calculatedColumnFormula>SUM(F:F)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{B3EDE8C1-FEE6-4401-BAF1-7A6A74F4FE86}" name="Hour Percent" dataDxfId="13" totalsRowDxfId="2">
+    <tableColumn id="3" xr3:uid="{B3EDE8C1-FEE6-4401-BAF1-7A6A74F4FE86}" name="Hour Percent" dataDxfId="11" totalsRowDxfId="10">
       <calculatedColumnFormula>Table2[[#This Row],[Total Minutes]]/60</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{8FB2D23B-72D8-4504-BE1A-A47C565D5166}" name="Hours Met" totalsRowFunction="custom" dataDxfId="12" totalsRowDxfId="1">
+    <tableColumn id="4" xr3:uid="{8FB2D23B-72D8-4504-BE1A-A47C565D5166}" name="Hours Met" totalsRowFunction="custom" dataDxfId="9" totalsRowDxfId="8">
       <calculatedColumnFormula>IF(Table2[[#This Row],[Hour Percent]] &gt;= Table2[[#This Row],[Hours Needed]], "Hours have been met", "More hours needed")</calculatedColumnFormula>
       <totalsRowFormula array="1">Table2[Hours Needed]-Table2[Hour Percent]</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{643AEBD5-F2A2-4877-923F-2A6F10830FA5}" name="Hours Needed" dataDxfId="11" totalsRowDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{643AEBD5-F2A2-4877-923F-2A6F10830FA5}" name="Hours Needed" dataDxfId="7" totalsRowDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{0B533ACD-D878-47CD-A04A-12CDF739F4F4}" name="Table3" displayName="Table3" ref="N2:Q12" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{0B533ACD-D878-47CD-A04A-12CDF739F4F4}" name="Table3" displayName="Table3" ref="N2:Q12" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
   <autoFilter ref="N2:Q12" xr:uid="{0B533ACD-D878-47CD-A04A-12CDF739F4F4}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{CFA6B21D-D050-4C14-8F9A-5D7117BEA113}" name="Weeks" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{1CA91632-7336-422D-ABF9-C5E3F08EFBA5}" name="Minutes" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{BB9EBBBA-CBEE-4ACF-8769-1D581F89C8FE}" name="Hours" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{8911D862-F455-4BFD-BDFF-6839D678C8CE}" name="Hour %" dataDxfId="5">
+    <tableColumn id="1" xr3:uid="{CFA6B21D-D050-4C14-8F9A-5D7117BEA113}" name="Weeks" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{1CA91632-7336-422D-ABF9-C5E3F08EFBA5}" name="Minutes" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{BB9EBBBA-CBEE-4ACF-8769-1D581F89C8FE}" name="Hours" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{8911D862-F455-4BFD-BDFF-6839D678C8CE}" name="Hour %" dataDxfId="0">
       <calculatedColumnFormula>O3/60</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -707,15 +707,15 @@
       </c>
       <c r="H3" s="1">
         <f>SUM(E:E) + (I3*60) + SUM(D:D)</f>
-        <v>11374</v>
+        <v>11629</v>
       </c>
       <c r="I3" s="6">
         <f>SUM(F:F)</f>
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="J3" s="5">
         <f>Table2[[#This Row],[Total Minutes]]/60</f>
-        <v>189.56666666666666</v>
+        <v>193.81666666666666</v>
       </c>
       <c r="K3" s="1" t="str">
         <f>IF(Table2[[#This Row],[Hour Percent]] &gt;= Table2[[#This Row],[Hours Needed]], "Hours have been met", "More hours needed")</f>
@@ -762,7 +762,7 @@
       <c r="J4" s="5"/>
       <c r="K4" s="5" cm="1">
         <f t="array" ref="K4">Table2[Hours Needed]-Table2[Hour Percent]</f>
-        <v>10.433333333333337</v>
+        <v>6.1833333333333371</v>
       </c>
       <c r="N4" s="1">
         <v>2</v>
@@ -837,11 +837,11 @@
       </c>
       <c r="H6" s="3">
         <f ca="1">NOW()</f>
-        <v>46085.575433101854</v>
+        <v>46086.635764930557</v>
       </c>
       <c r="I6" s="4">
         <f ca="1">NOW()</f>
-        <v>46085.575433101854</v>
+        <v>46086.635764930557</v>
       </c>
       <c r="N6" s="1">
         <v>4</v>
@@ -1018,15 +1018,15 @@
       </c>
       <c r="O11" s="6">
         <f>SUM(D59:E65) + (60*P11)</f>
-        <v>824</v>
+        <v>1079</v>
       </c>
       <c r="P11" s="6">
         <f>SUM(F59:F65)</f>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Q11" s="5">
         <f t="shared" si="0"/>
-        <v>13.733333333333333</v>
+        <v>17.983333333333334</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.35">
@@ -2000,32 +2000,38 @@
       <c r="B61" s="2">
         <v>46085.573803009262</v>
       </c>
-      <c r="C61" s="2"/>
+      <c r="C61" s="2">
+        <v>46085.633039236112</v>
+      </c>
       <c r="D61" s="5">
         <v>5</v>
       </c>
       <c r="E61" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F61" s="5">
         <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" s="7">
         <v>46086</v>
       </c>
-      <c r="B62" s="2"/>
-      <c r="C62" s="2"/>
+      <c r="B62" s="2">
+        <v>46086.591332523145</v>
+      </c>
+      <c r="C62" s="2">
+        <v>46086.709502314814</v>
+      </c>
       <c r="E62" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F62" s="5">
         <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.35">

--- a/Baseline_docs/Time Sheet.xlsx
+++ b/Baseline_docs/Time Sheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wskinner\On Drive Files\Git\Secure-Multi-Layer-Network-Project---Capstone\Baseline_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EB38C69-F4D6-4EC5-8EE8-C998D3C11772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBB91A43-2EA2-48ED-9DBE-CDE8B1DC6254}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1140" yWindow="1140" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -707,15 +707,15 @@
       </c>
       <c r="H3" s="1">
         <f>SUM(E:E) + (I3*60) + SUM(D:D)</f>
-        <v>11629</v>
+        <v>11750</v>
       </c>
       <c r="I3" s="6">
         <f>SUM(F:F)</f>
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="J3" s="5">
         <f>Table2[[#This Row],[Total Minutes]]/60</f>
-        <v>193.81666666666666</v>
+        <v>195.83333333333334</v>
       </c>
       <c r="K3" s="1" t="str">
         <f>IF(Table2[[#This Row],[Hour Percent]] &gt;= Table2[[#This Row],[Hours Needed]], "Hours have been met", "More hours needed")</f>
@@ -762,7 +762,7 @@
       <c r="J4" s="5"/>
       <c r="K4" s="5" cm="1">
         <f t="array" ref="K4">Table2[Hours Needed]-Table2[Hour Percent]</f>
-        <v>6.1833333333333371</v>
+        <v>4.1666666666666572</v>
       </c>
       <c r="N4" s="1">
         <v>2</v>
@@ -837,11 +837,11 @@
       </c>
       <c r="H6" s="3">
         <f ca="1">NOW()</f>
-        <v>46086.635764930557</v>
+        <v>46087.53997662037</v>
       </c>
       <c r="I6" s="4">
         <f ca="1">NOW()</f>
-        <v>46086.635764930557</v>
+        <v>46087.53997662037</v>
       </c>
       <c r="N6" s="1">
         <v>4</v>
@@ -1018,15 +1018,15 @@
       </c>
       <c r="O11" s="6">
         <f>SUM(D59:E65) + (60*P11)</f>
-        <v>1079</v>
+        <v>1200</v>
       </c>
       <c r="P11" s="6">
         <f>SUM(F59:F65)</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q11" s="5">
         <f t="shared" si="0"/>
-        <v>17.983333333333334</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.35">
@@ -2038,15 +2038,22 @@
       <c r="A63" s="7">
         <v>46087</v>
       </c>
-      <c r="B63" s="2"/>
-      <c r="C63" s="2"/>
+      <c r="B63" s="4">
+        <v>46087.4624744213</v>
+      </c>
+      <c r="C63" s="2">
+        <v>46087.539856597221</v>
+      </c>
+      <c r="D63" s="5">
+        <v>10</v>
+      </c>
       <c r="E63" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="F63" s="5">
         <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">

--- a/Baseline_docs/Time Sheet.xlsx
+++ b/Baseline_docs/Time Sheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wskinner\On Drive Files\Git\Secure-Multi-Layer-Network-Project---Capstone\Baseline_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBB91A43-2EA2-48ED-9DBE-CDE8B1DC6254}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77982D9E-CEB2-4FFC-869D-5AE68D92A0CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1140" yWindow="1140" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -707,19 +707,19 @@
       </c>
       <c r="H3" s="1">
         <f>SUM(E:E) + (I3*60) + SUM(D:D)</f>
-        <v>11750</v>
+        <v>12020</v>
       </c>
       <c r="I3" s="6">
         <f>SUM(F:F)</f>
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="J3" s="5">
         <f>Table2[[#This Row],[Total Minutes]]/60</f>
-        <v>195.83333333333334</v>
+        <v>200.33333333333334</v>
       </c>
       <c r="K3" s="1" t="str">
         <f>IF(Table2[[#This Row],[Hour Percent]] &gt;= Table2[[#This Row],[Hours Needed]], "Hours have been met", "More hours needed")</f>
-        <v>More hours needed</v>
+        <v>Hours have been met</v>
       </c>
       <c r="L3" s="1">
         <v>200</v>
@@ -762,7 +762,7 @@
       <c r="J4" s="5"/>
       <c r="K4" s="5" cm="1">
         <f t="array" ref="K4">Table2[Hours Needed]-Table2[Hour Percent]</f>
-        <v>4.1666666666666572</v>
+        <v>-0.33333333333334281</v>
       </c>
       <c r="N4" s="1">
         <v>2</v>
@@ -837,11 +837,11 @@
       </c>
       <c r="H6" s="3">
         <f ca="1">NOW()</f>
-        <v>46087.53997662037</v>
+        <v>46091.560033796297</v>
       </c>
       <c r="I6" s="4">
         <f ca="1">NOW()</f>
-        <v>46087.53997662037</v>
+        <v>46091.560033796297</v>
       </c>
       <c r="N6" s="1">
         <v>4</v>
@@ -1018,15 +1018,15 @@
       </c>
       <c r="O11" s="6">
         <f>SUM(D59:E65) + (60*P11)</f>
-        <v>1200</v>
+        <v>1380</v>
       </c>
       <c r="P11" s="6">
         <f>SUM(F59:F65)</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="Q11" s="5">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.35">
@@ -1052,15 +1052,15 @@
       </c>
       <c r="O12" s="6">
         <f>SUM(D66:E72) + (60*P12)</f>
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="P12" s="6">
         <f>SUM(F66:F72)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q12" s="5">
         <f>O12/60</f>
-        <v>0</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.35">
@@ -2060,45 +2060,57 @@
       <c r="A64" s="7">
         <v>46088</v>
       </c>
-      <c r="B64" s="2"/>
-      <c r="C64" s="2"/>
+      <c r="B64" s="2">
+        <v>46088.583611111113</v>
+      </c>
+      <c r="C64" s="2">
+        <v>46088.646111111113</v>
+      </c>
       <c r="E64" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F64" s="5">
         <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" s="7">
         <v>46089</v>
       </c>
-      <c r="B65" s="2"/>
-      <c r="C65" s="2"/>
+      <c r="B65" s="2">
+        <v>46089.583611111113</v>
+      </c>
+      <c r="C65" s="2">
+        <v>46089.646111111113</v>
+      </c>
       <c r="E65" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F65" s="5">
         <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" s="7">
         <v>46090</v>
       </c>
-      <c r="B66" s="2"/>
-      <c r="C66" s="2"/>
+      <c r="B66" s="2">
+        <v>46090.583611111113</v>
+      </c>
+      <c r="C66" s="2">
+        <v>46090.646111111113</v>
+      </c>
       <c r="E66" s="5">
         <f>IFERROR(MINUTE((Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]])),0)</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F66" s="5">
         <f>IFERROR(HOUR(Table1[[#This Row],[Stop]]-Table1[[#This Row],[Start]]),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
